--- a/Contador de Pagina Oficina Julio del 01 al 31.xlsx
+++ b/Contador de Pagina Oficina Julio del 01 al 31.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\MXL30618CB\c606409\Documents\Respaldo Siffs\11.- PREVENTIVO TORRE- REGION\Contadores de Pagina Mensual\2026\7.- Julio 2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin-c606401\Documents\hp\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -8956,612 +8956,7 @@
     <cellStyle name="Título 3" xfId="4" builtinId="18" customBuiltin="1"/>
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="783">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="728">
     <dxf>
       <font>
         <b/>
@@ -22059,7 +21454,7 @@
         <v>191</v>
       </c>
       <c r="T2" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U2" s="14"/>
       <c r="V2" s="108" t="s">
@@ -22130,7 +21525,7 @@
         <v>194</v>
       </c>
       <c r="T3" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U3" s="14"/>
       <c r="V3" s="108" t="s">
@@ -22201,7 +21596,7 @@
         <v>582</v>
       </c>
       <c r="T4" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U4" s="57"/>
       <c r="V4" s="105" t="s">
@@ -22272,7 +21667,7 @@
         <v>0</v>
       </c>
       <c r="T5" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U5" s="14" t="s">
         <v>2126</v>
@@ -22345,7 +21740,7 @@
         <v>0</v>
       </c>
       <c r="T6" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U6" s="14"/>
       <c r="V6" s="105" t="s">
@@ -22415,7 +21810,7 @@
         <v>0</v>
       </c>
       <c r="T7" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U7" s="14" t="s">
         <v>2086</v>
@@ -22488,7 +21883,7 @@
         <v>469</v>
       </c>
       <c r="T8" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U8" s="14" t="s">
         <v>2437</v>
@@ -22561,7 +21956,7 @@
         <v>2390</v>
       </c>
       <c r="T9" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U9" s="14"/>
       <c r="V9" s="108" t="s">
@@ -22632,7 +22027,7 @@
         <v>11</v>
       </c>
       <c r="T10" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U10" s="14" t="s">
         <v>2429</v>
@@ -22705,7 +22100,7 @@
         <v>539</v>
       </c>
       <c r="T11" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U11" s="14"/>
       <c r="V11" s="105" t="s">
@@ -22776,7 +22171,7 @@
         <v>235</v>
       </c>
       <c r="T12" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U12" s="14"/>
       <c r="V12" s="105" t="s">
@@ -22847,7 +22242,7 @@
         <v>381</v>
       </c>
       <c r="T13" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U13" s="14"/>
       <c r="V13" s="108" t="s">
@@ -22918,7 +22313,7 @@
         <v>0</v>
       </c>
       <c r="T14" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U14" s="14"/>
       <c r="V14" s="105" t="s">
@@ -22989,7 +22384,7 @@
         <v>27</v>
       </c>
       <c r="T15" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U15" s="14"/>
       <c r="V15" s="105" t="s">
@@ -23060,7 +22455,7 @@
         <v>0</v>
       </c>
       <c r="T16" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U16" s="14" t="s">
         <v>2470</v>
@@ -23132,7 +22527,7 @@
         <v>808</v>
       </c>
       <c r="T17" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U17" s="57"/>
       <c r="V17" s="108" t="s">
@@ -23203,7 +22598,7 @@
         <v>4780</v>
       </c>
       <c r="T18" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U18" s="14"/>
       <c r="V18" s="105" t="s">
@@ -23274,7 +22669,7 @@
         <v>0</v>
       </c>
       <c r="T19" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U19" s="14" t="s">
         <v>2454</v>
@@ -23347,7 +22742,7 @@
         <v>44</v>
       </c>
       <c r="T20" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U20" s="14"/>
       <c r="V20" s="105" t="s">
@@ -23418,7 +22813,7 @@
         <v>834</v>
       </c>
       <c r="T21" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U21" s="14"/>
       <c r="V21" s="105" t="s">
@@ -23489,7 +22884,7 @@
         <v>0</v>
       </c>
       <c r="T22" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U22" s="14"/>
       <c r="V22" s="105" t="s">
@@ -23560,7 +22955,7 @@
         <v>658</v>
       </c>
       <c r="T23" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U23" s="14"/>
       <c r="V23" s="105" t="s">
@@ -23631,7 +23026,7 @@
         <v>2046</v>
       </c>
       <c r="T24" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U24" s="14"/>
       <c r="V24" s="105" t="s">
@@ -23702,7 +23097,7 @@
         <v>199</v>
       </c>
       <c r="T25" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U25" s="14"/>
       <c r="V25" s="105" t="s">
@@ -23773,7 +23168,7 @@
         <v>3628</v>
       </c>
       <c r="T26" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U26" s="14"/>
       <c r="V26" s="105" t="s">
@@ -23844,7 +23239,7 @@
         <v>649</v>
       </c>
       <c r="T27" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U27" s="14"/>
       <c r="V27" s="105" t="s">
@@ -23915,7 +23310,7 @@
         <v>0</v>
       </c>
       <c r="T28" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U28" s="14"/>
       <c r="V28" s="105" t="s">
@@ -23986,7 +23381,7 @@
         <v>1396</v>
       </c>
       <c r="T29" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U29" s="14"/>
       <c r="V29" s="105" t="s">
@@ -24057,7 +23452,7 @@
         <v>0</v>
       </c>
       <c r="T30" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U30" s="14" t="s">
         <v>2397</v>
@@ -24130,7 +23525,7 @@
         <v>651</v>
       </c>
       <c r="T31" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U31" s="14"/>
       <c r="V31" s="105" t="s">
@@ -24201,7 +23596,7 @@
         <v>0</v>
       </c>
       <c r="T32" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U32" s="14" t="s">
         <v>2468</v>
@@ -24274,7 +23669,7 @@
         <v>104</v>
       </c>
       <c r="T33" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U33" s="14"/>
       <c r="V33" s="105" t="s">
@@ -24345,7 +23740,7 @@
         <v>0</v>
       </c>
       <c r="T34" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U34" s="14"/>
       <c r="V34" s="105" t="s">
@@ -24416,7 +23811,7 @@
         <v>0</v>
       </c>
       <c r="T35" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U35" s="14"/>
       <c r="V35" s="105" t="s">
@@ -24487,7 +23882,7 @@
         <v>783</v>
       </c>
       <c r="T36" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U36" s="14"/>
       <c r="V36" s="108" t="s">
@@ -24558,7 +23953,7 @@
         <v>272</v>
       </c>
       <c r="T37" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U37" s="14"/>
       <c r="V37" s="108" t="s">
@@ -24629,7 +24024,7 @@
         <v>0</v>
       </c>
       <c r="T38" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U38" s="14"/>
       <c r="V38" s="105" t="s">
@@ -24700,7 +24095,7 @@
         <v>1015</v>
       </c>
       <c r="T39" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U39" s="14"/>
       <c r="V39" s="105" t="s">
@@ -24771,7 +24166,7 @@
         <v>0</v>
       </c>
       <c r="T40" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U40" s="14" t="s">
         <v>2166</v>
@@ -24844,7 +24239,7 @@
         <v>0</v>
       </c>
       <c r="T41" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U41" s="14" t="s">
         <v>2166</v>
@@ -24917,7 +24312,7 @@
         <v>152</v>
       </c>
       <c r="T42" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U42" s="57"/>
       <c r="V42" s="105" t="s">
@@ -24988,7 +24383,7 @@
         <v>1097</v>
       </c>
       <c r="T43" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U43" s="57"/>
       <c r="V43" s="108" t="s">
@@ -25059,7 +24454,7 @@
         <v>875</v>
       </c>
       <c r="T44" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U44" s="57"/>
       <c r="V44" s="108" t="s">
@@ -25130,7 +24525,7 @@
         <v>1405</v>
       </c>
       <c r="T45" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U45" s="14"/>
       <c r="V45" s="108" t="s">
@@ -25201,7 +24596,7 @@
         <v>919</v>
       </c>
       <c r="T46" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U46" s="14"/>
       <c r="V46" s="105" t="s">
@@ -25272,7 +24667,7 @@
         <v>2088</v>
       </c>
       <c r="T47" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U47" s="14"/>
       <c r="V47" s="105" t="s">
@@ -25343,7 +24738,7 @@
         <v>6826</v>
       </c>
       <c r="T48" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U48" s="14"/>
       <c r="V48" s="105" t="s">
@@ -25414,7 +24809,7 @@
         <v>0</v>
       </c>
       <c r="T49" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U49" s="14" t="s">
         <v>2080</v>
@@ -25487,7 +24882,7 @@
         <v>0</v>
       </c>
       <c r="T50" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U50" s="14"/>
       <c r="V50" s="105" t="s">
@@ -25558,7 +24953,7 @@
         <v>0</v>
       </c>
       <c r="T51" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U51" s="14" t="s">
         <v>2469</v>
@@ -25628,7 +25023,7 @@
         <v>0</v>
       </c>
       <c r="T52" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U52" s="14" t="s">
         <v>2427</v>
@@ -25700,7 +25095,7 @@
         <v>2137</v>
       </c>
       <c r="T53" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U53" s="14" t="s">
         <v>2440</v>
@@ -25772,7 +25167,7 @@
         <v>0</v>
       </c>
       <c r="T54" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U54" s="14"/>
       <c r="V54" s="105" t="s">
@@ -25843,7 +25238,7 @@
         <v>1280</v>
       </c>
       <c r="T55" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U55" s="14"/>
       <c r="V55" s="105" t="s">
@@ -25914,7 +25309,7 @@
         <v>0</v>
       </c>
       <c r="T56" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U56" s="14" t="s">
         <v>2389</v>
@@ -25987,7 +25382,7 @@
         <v>5154</v>
       </c>
       <c r="T57" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U57" s="14"/>
       <c r="V57" s="105" t="s">
@@ -26056,7 +25451,7 @@
         <v>0</v>
       </c>
       <c r="T58" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U58" s="14" t="s">
         <v>2486</v>
@@ -26129,7 +25524,7 @@
         <v>0</v>
       </c>
       <c r="T59" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U59" s="14" t="s">
         <v>2125</v>
@@ -26202,7 +25597,7 @@
         <v>1122</v>
       </c>
       <c r="T60" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U60" s="14"/>
       <c r="V60" s="108" t="s">
@@ -26271,7 +25666,7 @@
         <v>0</v>
       </c>
       <c r="T61" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U61" s="14" t="s">
         <v>2103</v>
@@ -26344,7 +25739,7 @@
         <v>1040</v>
       </c>
       <c r="T62" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U62" s="14"/>
       <c r="V62" s="105" t="s">
@@ -26415,7 +25810,7 @@
         <v>0</v>
       </c>
       <c r="T63" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U63" s="14"/>
       <c r="V63" s="105" t="s">
@@ -26486,7 +25881,7 @@
         <v>0</v>
       </c>
       <c r="T64" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U64" s="14"/>
       <c r="V64" s="105" t="s">
@@ -26555,7 +25950,7 @@
         <v>0</v>
       </c>
       <c r="T65" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U65" s="8" t="s">
         <v>2381</v>
@@ -26626,7 +26021,7 @@
         <v>0</v>
       </c>
       <c r="T66" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U66" s="14" t="s">
         <v>2391</v>
@@ -26699,7 +26094,7 @@
         <v>1817</v>
       </c>
       <c r="T67" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U67" s="14"/>
       <c r="V67" s="105" t="s">
@@ -26770,7 +26165,7 @@
         <v>1257</v>
       </c>
       <c r="T68" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U68" s="57"/>
       <c r="V68" s="105" t="s">
@@ -26841,7 +26236,7 @@
         <v>2289</v>
       </c>
       <c r="T69" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U69" s="14"/>
       <c r="V69" s="105" t="s">
@@ -26912,7 +26307,7 @@
         <v>0</v>
       </c>
       <c r="T70" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U70" s="14"/>
       <c r="V70" s="105" t="s">
@@ -26983,7 +26378,7 @@
         <v>577</v>
       </c>
       <c r="T71" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U71" s="14"/>
       <c r="V71" s="105" t="s">
@@ -27053,7 +26448,7 @@
         <v>0</v>
       </c>
       <c r="T72" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U72" s="14" t="s">
         <v>2188</v>
@@ -27126,7 +26521,7 @@
         <v>1033</v>
       </c>
       <c r="T73" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U73" s="14"/>
       <c r="V73" s="105" t="s">
@@ -27197,7 +26592,7 @@
         <v>1081</v>
       </c>
       <c r="T74" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U74" s="14"/>
       <c r="V74" s="105" t="s">
@@ -27268,7 +26663,7 @@
         <v>787</v>
       </c>
       <c r="T75" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U75" s="14"/>
       <c r="V75" s="105" t="s">
@@ -27339,7 +26734,7 @@
         <v>288</v>
       </c>
       <c r="T76" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U76" s="14"/>
       <c r="V76" s="105" t="s">
@@ -27410,7 +26805,7 @@
         <v>1544</v>
       </c>
       <c r="T77" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U77" s="14"/>
       <c r="V77" s="105" t="s">
@@ -27481,7 +26876,7 @@
         <v>0</v>
       </c>
       <c r="T78" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U78" s="14" t="s">
         <v>2151</v>
@@ -27554,7 +26949,7 @@
         <v>0</v>
       </c>
       <c r="T79" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U79" s="53" t="s">
         <v>2150</v>
@@ -27627,7 +27022,7 @@
         <v>0</v>
       </c>
       <c r="T80" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U80" s="14" t="s">
         <v>2209</v>
@@ -27700,7 +27095,7 @@
         <v>2504</v>
       </c>
       <c r="T81" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U81" s="14"/>
       <c r="V81" s="105" t="s">
@@ -27771,7 +27166,7 @@
         <v>1266</v>
       </c>
       <c r="T82" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U82" s="14"/>
       <c r="V82" s="105" t="s">
@@ -27842,7 +27237,7 @@
         <v>3001</v>
       </c>
       <c r="T83" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U83" s="14"/>
       <c r="V83" s="105" t="s">
@@ -27913,7 +27308,7 @@
         <v>68</v>
       </c>
       <c r="T84" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U84" s="14" t="s">
         <v>2392</v>
@@ -27986,7 +27381,7 @@
         <v>0</v>
       </c>
       <c r="T85" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U85" s="14" t="s">
         <v>2455</v>
@@ -28059,7 +27454,7 @@
         <v>0</v>
       </c>
       <c r="T86" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U86" s="14" t="s">
         <v>2132</v>
@@ -28130,7 +27525,7 @@
         <v>0</v>
       </c>
       <c r="T87" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U87" s="14" t="s">
         <v>2408</v>
@@ -28203,7 +27598,7 @@
         <v>0</v>
       </c>
       <c r="T88" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U88" s="14"/>
       <c r="V88" s="105" t="s">
@@ -28274,7 +27669,7 @@
         <v>282</v>
       </c>
       <c r="T89" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U89" s="14" t="s">
         <v>2465</v>
@@ -28347,7 +27742,7 @@
         <v>522</v>
       </c>
       <c r="T90" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U90" s="14"/>
       <c r="V90" s="105" t="s">
@@ -28418,7 +27813,7 @@
         <v>605</v>
       </c>
       <c r="T91" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U91" s="14"/>
       <c r="V91" s="105" t="s">
@@ -28489,7 +27884,7 @@
         <v>0</v>
       </c>
       <c r="T92" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U92" s="14"/>
       <c r="V92" s="105" t="s">
@@ -28560,7 +27955,7 @@
         <v>418</v>
       </c>
       <c r="T93" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U93" s="14"/>
       <c r="V93" s="105" t="s">
@@ -28631,7 +28026,7 @@
         <v>1404</v>
       </c>
       <c r="T94" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U94" s="14"/>
       <c r="V94" s="105" t="s">
@@ -28702,7 +28097,7 @@
         <v>979</v>
       </c>
       <c r="T95" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U95" s="14"/>
       <c r="V95" s="105" t="s">
@@ -28773,7 +28168,7 @@
         <v>0</v>
       </c>
       <c r="T96" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U96" s="14"/>
       <c r="V96" s="105" t="s">
@@ -28844,7 +28239,7 @@
         <v>0</v>
       </c>
       <c r="T97" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U97" s="14"/>
       <c r="V97" s="105" t="s">
@@ -28915,7 +28310,7 @@
         <v>720</v>
       </c>
       <c r="T98" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U98" s="14"/>
       <c r="V98" s="108" t="s">
@@ -28986,7 +28381,7 @@
         <v>4798</v>
       </c>
       <c r="T99" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U99" s="14"/>
       <c r="V99" s="105" t="s">
@@ -29057,7 +28452,7 @@
         <v>0</v>
       </c>
       <c r="T100" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U100" s="14" t="s">
         <v>2403</v>
@@ -29130,7 +28525,7 @@
         <v>0</v>
       </c>
       <c r="T101" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U101" s="14" t="s">
         <v>2478</v>
@@ -29203,7 +28598,7 @@
         <v>356</v>
       </c>
       <c r="T102" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U102" s="14"/>
       <c r="V102" s="105" t="s">
@@ -29274,7 +28669,7 @@
         <v>1349</v>
       </c>
       <c r="T103" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U103" s="14"/>
       <c r="V103" s="105" t="s">
@@ -29345,7 +28740,7 @@
         <v>302</v>
       </c>
       <c r="T104" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U104" s="14" t="s">
         <v>2477</v>
@@ -29418,7 +28813,7 @@
         <v>2701</v>
       </c>
       <c r="T105" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U105" s="14"/>
       <c r="V105" s="105" t="s">
@@ -29489,7 +28884,7 @@
         <v>210</v>
       </c>
       <c r="T106" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U106" s="14"/>
       <c r="V106" s="105" t="s">
@@ -29560,7 +28955,7 @@
         <v>308</v>
       </c>
       <c r="T107" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U107" s="14"/>
       <c r="V107" s="105" t="s">
@@ -29631,7 +29026,7 @@
         <v>1426</v>
       </c>
       <c r="T108" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U108" s="54"/>
       <c r="V108" s="105" t="s">
@@ -29702,7 +29097,7 @@
         <v>0</v>
       </c>
       <c r="T109" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U109" s="14"/>
       <c r="V109" s="105" t="s">
@@ -29773,7 +29168,7 @@
         <v>600</v>
       </c>
       <c r="T110" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U110" s="14"/>
       <c r="V110" s="105" t="s">
@@ -29844,7 +29239,7 @@
         <v>0</v>
       </c>
       <c r="T111" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U111" s="14" t="s">
         <v>2456</v>
@@ -29917,7 +29312,7 @@
         <v>285</v>
       </c>
       <c r="T112" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U112" s="14"/>
       <c r="V112" s="105" t="s">
@@ -29985,7 +29380,7 @@
         <v>0</v>
       </c>
       <c r="T113" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U113" s="14" t="s">
         <v>2498</v>
@@ -30056,7 +29451,7 @@
         <v>0</v>
       </c>
       <c r="T114" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U114" s="14" t="s">
         <v>2462</v>
@@ -30128,7 +29523,7 @@
         <v>435</v>
       </c>
       <c r="T115" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U115" s="14"/>
       <c r="V115" s="105" t="s">
@@ -30199,7 +29594,7 @@
         <v>770</v>
       </c>
       <c r="T116" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U116" s="14"/>
       <c r="V116" s="105" t="s">
@@ -30268,7 +29663,7 @@
         <v>0</v>
       </c>
       <c r="T117" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U117" s="118" t="s">
         <v>2420</v>
@@ -30341,7 +29736,7 @@
         <v>0</v>
       </c>
       <c r="T118" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U118" s="14" t="s">
         <v>2395</v>
@@ -30414,7 +29809,7 @@
         <v>0</v>
       </c>
       <c r="T119" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U119" s="14"/>
       <c r="V119" s="105" t="s">
@@ -30485,7 +29880,7 @@
         <v>584</v>
       </c>
       <c r="T120" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U120" s="14"/>
       <c r="V120" s="105" t="s">
@@ -30556,7 +29951,7 @@
         <v>1816</v>
       </c>
       <c r="T121" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U121" s="14" t="s">
         <v>2447</v>
@@ -30627,7 +30022,7 @@
         <v>0</v>
       </c>
       <c r="T122" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U122" s="14" t="s">
         <v>2127</v>
@@ -30700,7 +30095,7 @@
         <v>0</v>
       </c>
       <c r="T123" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U123" s="14" t="s">
         <v>2396</v>
@@ -30773,7 +30168,7 @@
         <v>0</v>
       </c>
       <c r="T124" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U124" s="13"/>
       <c r="V124" s="105" t="s">
@@ -30843,7 +30238,7 @@
         <v>2892</v>
       </c>
       <c r="T125" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U125" s="14"/>
       <c r="V125" s="105" t="s">
@@ -30913,7 +30308,7 @@
         <v>1566</v>
       </c>
       <c r="T126" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U126" s="14"/>
       <c r="V126" s="105" t="s">
@@ -30984,7 +30379,7 @@
         <v>0</v>
       </c>
       <c r="T127" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U127" s="14" t="s">
         <v>2393</v>
@@ -31056,7 +30451,7 @@
         <v>359</v>
       </c>
       <c r="T128" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U128" s="14"/>
       <c r="V128" s="105" t="s">
@@ -31127,7 +30522,7 @@
         <v>1525</v>
       </c>
       <c r="T129" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U129" s="14"/>
       <c r="V129" s="105" t="s">
@@ -31198,7 +30593,7 @@
         <v>18347</v>
       </c>
       <c r="T130" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U130" s="14"/>
       <c r="V130" s="105" t="s">
@@ -31269,7 +30664,7 @@
         <v>7001</v>
       </c>
       <c r="T131" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U131" s="14"/>
       <c r="V131" s="105" t="s">
@@ -31340,7 +30735,7 @@
         <v>5899</v>
       </c>
       <c r="T132" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U132" s="14"/>
       <c r="V132" s="105" t="s">
@@ -31411,7 +30806,7 @@
         <v>0</v>
       </c>
       <c r="T133" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U133" s="14"/>
       <c r="V133" s="105" t="s">
@@ -31482,7 +30877,7 @@
         <v>4800</v>
       </c>
       <c r="T134" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U134" s="14"/>
       <c r="V134" s="105" t="s">
@@ -31553,7 +30948,7 @@
         <v>0</v>
       </c>
       <c r="T135" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U135" s="14"/>
       <c r="V135" s="105" t="s">
@@ -31624,7 +31019,7 @@
         <v>0</v>
       </c>
       <c r="T136" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U136" s="14"/>
       <c r="V136" s="105" t="s">
@@ -31694,7 +31089,7 @@
         <v>10132</v>
       </c>
       <c r="T137" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U137" s="14"/>
       <c r="V137" s="105" t="s">
@@ -31765,7 +31160,7 @@
         <v>349</v>
       </c>
       <c r="T138" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U138" s="14"/>
       <c r="V138" s="105" t="s">
@@ -31836,7 +31231,7 @@
         <v>493</v>
       </c>
       <c r="T139" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U139" s="14"/>
       <c r="V139" s="108" t="s">
@@ -31908,7 +31303,7 @@
         <v>2808</v>
       </c>
       <c r="T140" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U140" s="14"/>
       <c r="V140" s="105" t="s">
@@ -31979,7 +31374,7 @@
         <v>11</v>
       </c>
       <c r="T141" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U141" s="14"/>
       <c r="V141" s="105" t="s">
@@ -32050,7 +31445,7 @@
         <v>5009</v>
       </c>
       <c r="T142" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U142" s="14"/>
       <c r="V142" s="105" t="s">
@@ -32121,7 +31516,7 @@
         <v>0</v>
       </c>
       <c r="T143" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U143" s="14" t="s">
         <v>2445</v>
@@ -32194,7 +31589,7 @@
         <v>0</v>
       </c>
       <c r="T144" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U144" s="14" t="s">
         <v>2445</v>
@@ -32267,7 +31662,7 @@
         <v>9931</v>
       </c>
       <c r="T145" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U145" s="14"/>
       <c r="V145" s="105" t="s">
@@ -32338,7 +31733,7 @@
         <v>0</v>
       </c>
       <c r="T146" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U146" s="14"/>
       <c r="V146" s="105" t="s">
@@ -32409,7 +31804,7 @@
         <v>4823</v>
       </c>
       <c r="T147" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U147" s="14"/>
       <c r="V147" s="105" t="s">
@@ -32480,7 +31875,7 @@
         <v>6391</v>
       </c>
       <c r="T148" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U148" s="14"/>
       <c r="V148" s="105" t="s">
@@ -32551,7 +31946,7 @@
         <v>0</v>
       </c>
       <c r="T149" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U149" s="14" t="s">
         <v>2471</v>
@@ -32623,7 +32018,7 @@
         <v>0</v>
       </c>
       <c r="T150" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U150" s="14" t="s">
         <v>2165</v>
@@ -32696,7 +32091,7 @@
         <v>0</v>
       </c>
       <c r="T151" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U151" s="14" t="s">
         <v>2029</v>
@@ -32769,7 +32164,7 @@
         <v>0</v>
       </c>
       <c r="T152" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U152" s="14" t="s">
         <v>2469</v>
@@ -32841,7 +32236,7 @@
         <v>16376</v>
       </c>
       <c r="T153" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U153" s="14"/>
       <c r="V153" s="105" t="s">
@@ -32912,7 +32307,7 @@
         <v>2841</v>
       </c>
       <c r="T154" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U154" s="14"/>
       <c r="V154" s="105" t="s">
@@ -32983,7 +32378,7 @@
         <v>0</v>
       </c>
       <c r="T155" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U155" s="14"/>
       <c r="V155" s="105" t="s">
@@ -33054,7 +32449,7 @@
         <v>5566</v>
       </c>
       <c r="T156" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U156" s="14"/>
       <c r="V156" s="105" t="s">
@@ -33125,7 +32520,7 @@
         <v>0</v>
       </c>
       <c r="T157" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U157" s="14" t="s">
         <v>2456</v>
@@ -33198,7 +32593,7 @@
         <v>0</v>
       </c>
       <c r="T158" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U158" s="14" t="s">
         <v>2460</v>
@@ -33271,7 +32666,7 @@
         <v>5450</v>
       </c>
       <c r="T159" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U159" s="14"/>
       <c r="V159" s="105" t="s">
@@ -33342,7 +32737,7 @@
         <v>0</v>
       </c>
       <c r="T160" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U160" s="14"/>
       <c r="V160" s="105" t="s">
@@ -33413,7 +32808,7 @@
         <v>8291</v>
       </c>
       <c r="T161" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U161" s="14"/>
       <c r="V161" s="108" t="s">
@@ -33484,7 +32879,7 @@
         <v>3830</v>
       </c>
       <c r="T162" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U162" s="14"/>
       <c r="V162" s="108" t="s">
@@ -33555,7 +32950,7 @@
         <v>0</v>
       </c>
       <c r="T163" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U163" s="14" t="s">
         <v>2415</v>
@@ -33628,7 +33023,7 @@
         <v>722</v>
       </c>
       <c r="T164" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U164" s="14" t="s">
         <v>2463</v>
@@ -33701,7 +33096,7 @@
         <v>5704</v>
       </c>
       <c r="T165" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U165" s="14"/>
       <c r="V165" s="105" t="s">
@@ -33770,7 +33165,7 @@
         <v>0</v>
       </c>
       <c r="T166" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U166" s="14" t="s">
         <v>2098</v>
@@ -33843,7 +33238,7 @@
         <v>0</v>
       </c>
       <c r="T167" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U167" s="14"/>
       <c r="V167" s="105" t="s">
@@ -33914,7 +33309,7 @@
         <v>2378</v>
       </c>
       <c r="T168" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U168" s="14"/>
       <c r="V168" s="105" t="s">
@@ -33985,7 +33380,7 @@
         <v>2297</v>
       </c>
       <c r="T169" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U169" s="14"/>
       <c r="V169" s="105" t="s">
@@ -34056,7 +33451,7 @@
         <v>4944</v>
       </c>
       <c r="T170" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U170" s="14"/>
       <c r="V170" s="108" t="s">
@@ -34127,7 +33522,7 @@
         <v>6905</v>
       </c>
       <c r="T171" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U171" s="14" t="s">
         <v>2452</v>
@@ -34199,7 +33594,7 @@
         <v>10495</v>
       </c>
       <c r="T172" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U172" s="14"/>
       <c r="V172" s="105" t="s">
@@ -34270,7 +33665,7 @@
         <v>4996</v>
       </c>
       <c r="T173" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U173" s="14"/>
       <c r="V173" s="108" t="s">
@@ -34341,7 +33736,7 @@
         <v>0</v>
       </c>
       <c r="T174" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U174" s="14"/>
       <c r="V174" s="105" t="s">
@@ -34412,7 +33807,7 @@
         <v>0</v>
       </c>
       <c r="T175" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U175" s="14"/>
       <c r="V175" s="105" t="s">
@@ -34483,7 +33878,7 @@
         <v>0</v>
       </c>
       <c r="T176" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U176" s="14"/>
       <c r="V176" s="105" t="s">
@@ -34554,7 +33949,7 @@
         <v>1656</v>
       </c>
       <c r="T177" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U177" s="14" t="s">
         <v>2475</v>
@@ -34626,7 +34021,7 @@
         <v>6401</v>
       </c>
       <c r="T178" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U178" s="14"/>
       <c r="V178" s="105" t="s">
@@ -34697,7 +34092,7 @@
         <v>10537</v>
       </c>
       <c r="T179" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U179" s="14"/>
       <c r="V179" s="105" t="s">
@@ -34768,7 +34163,7 @@
         <v>585</v>
       </c>
       <c r="T180" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U180" s="14" t="s">
         <v>2483</v>
@@ -34841,7 +34236,7 @@
         <v>0</v>
       </c>
       <c r="T181" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U181" s="14"/>
       <c r="V181" s="105" t="s">
@@ -34912,7 +34307,7 @@
         <v>5644</v>
       </c>
       <c r="T182" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U182" s="14"/>
       <c r="V182" s="105" t="s">
@@ -34983,7 +34378,7 @@
         <v>4869</v>
       </c>
       <c r="T183" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U183" s="14"/>
       <c r="V183" s="105" t="s">
@@ -35054,7 +34449,7 @@
         <v>8639</v>
       </c>
       <c r="T184" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U184" s="14"/>
       <c r="V184" s="105" t="s">
@@ -35125,7 +34520,7 @@
         <v>5167</v>
       </c>
       <c r="T185" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U185" s="93" t="s">
         <v>2488</v>
@@ -35198,7 +34593,7 @@
         <v>6862</v>
       </c>
       <c r="T186" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U186" s="14"/>
       <c r="V186" s="105" t="s">
@@ -35269,7 +34664,7 @@
         <v>1179</v>
       </c>
       <c r="T187" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U187" s="84"/>
       <c r="V187" s="115" t="s">
@@ -35340,7 +34735,7 @@
         <v>5877</v>
       </c>
       <c r="T188" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U188" s="54" t="s">
         <v>2419</v>
@@ -35410,7 +34805,7 @@
         <v>0</v>
       </c>
       <c r="T189" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U189" s="13" t="s">
         <v>2457</v>
@@ -35483,7 +34878,7 @@
         <v>0</v>
       </c>
       <c r="T190" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U190" s="14"/>
       <c r="V190" s="105" t="s">
@@ -35554,7 +34949,7 @@
         <v>0</v>
       </c>
       <c r="T191" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U191" s="14"/>
       <c r="V191" s="105" t="s">
@@ -35623,7 +35018,7 @@
         <v>0</v>
       </c>
       <c r="T192" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U192" s="14"/>
       <c r="V192" s="105" t="s">
@@ -35694,7 +35089,7 @@
         <v>1878</v>
       </c>
       <c r="T193" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U193" s="14"/>
       <c r="V193" s="105" t="s">
@@ -35765,7 +35160,7 @@
         <v>4851</v>
       </c>
       <c r="T194" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U194" s="14"/>
       <c r="V194" s="105" t="s">
@@ -35836,7 +35231,7 @@
         <v>3521</v>
       </c>
       <c r="T195" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U195" s="14"/>
       <c r="V195" s="105" t="s">
@@ -35907,7 +35302,7 @@
         <v>0</v>
       </c>
       <c r="T196" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U196" s="14"/>
       <c r="V196" s="105" t="s">
@@ -35976,7 +35371,7 @@
         <v>0</v>
       </c>
       <c r="T197" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U197" s="14" t="s">
         <v>2222</v>
@@ -36049,7 +35444,7 @@
         <v>19751</v>
       </c>
       <c r="T198" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U198" s="14"/>
       <c r="V198" s="105" t="s">
@@ -36120,7 +35515,7 @@
         <v>0</v>
       </c>
       <c r="T199" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U199" s="14" t="s">
         <v>2033</v>
@@ -36193,7 +35588,7 @@
         <v>5615</v>
       </c>
       <c r="T200" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U200" s="14"/>
       <c r="V200" s="105" t="s">
@@ -36264,7 +35659,7 @@
         <v>8417</v>
       </c>
       <c r="T201" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U201" s="14"/>
       <c r="V201" s="105" t="s">
@@ -36335,7 +35730,7 @@
         <v>16531</v>
       </c>
       <c r="T202" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U202" s="14"/>
       <c r="V202" s="105" t="s">
@@ -36406,7 +35801,7 @@
         <v>0</v>
       </c>
       <c r="T203" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U203" s="14"/>
       <c r="V203" s="105" t="s">
@@ -36477,7 +35872,7 @@
         <v>0</v>
       </c>
       <c r="T204" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U204" s="14"/>
       <c r="V204" s="105" t="s">
@@ -36548,7 +35943,7 @@
         <v>8376</v>
       </c>
       <c r="T205" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U205" s="14"/>
       <c r="V205" s="105" t="s">
@@ -36619,7 +36014,7 @@
         <v>8247</v>
       </c>
       <c r="T206" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U206" s="14"/>
       <c r="V206" s="105" t="s">
@@ -36690,7 +36085,7 @@
         <v>825</v>
       </c>
       <c r="T207" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U207" s="14"/>
       <c r="V207" s="105" t="s">
@@ -36761,7 +36156,7 @@
         <v>0</v>
       </c>
       <c r="T208" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U208" s="14"/>
       <c r="V208" s="108" t="s">
@@ -36832,7 +36227,7 @@
         <v>1689</v>
       </c>
       <c r="T209" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U209" s="14"/>
       <c r="V209" s="105" t="s">
@@ -36903,7 +36298,7 @@
         <v>2757</v>
       </c>
       <c r="T210" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U210" s="14"/>
       <c r="V210" s="105" t="s">
@@ -36974,7 +36369,7 @@
         <v>0</v>
       </c>
       <c r="T211" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U211" s="14"/>
       <c r="V211" s="105" t="s">
@@ -37043,7 +36438,7 @@
         <v>0</v>
       </c>
       <c r="T212" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U212" s="105" t="s">
         <v>2458</v>
@@ -37116,7 +36511,7 @@
         <v>2635</v>
       </c>
       <c r="T213" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U213" s="14"/>
       <c r="V213" s="105" t="s">
@@ -37187,7 +36582,7 @@
         <v>5636</v>
       </c>
       <c r="T214" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U214" s="14"/>
       <c r="V214" s="105" t="s">
@@ -37258,7 +36653,7 @@
         <v>0</v>
       </c>
       <c r="T215" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U215" s="14"/>
       <c r="V215" s="105" t="s">
@@ -37329,7 +36724,7 @@
         <v>7180</v>
       </c>
       <c r="T216" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U216" s="14"/>
       <c r="V216" s="105" t="s">
@@ -37399,7 +36794,7 @@
         <v>0</v>
       </c>
       <c r="T217" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U217" s="14" t="s">
         <v>2459</v>
@@ -37472,7 +36867,7 @@
         <v>662</v>
       </c>
       <c r="T218" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U218" s="14"/>
       <c r="V218" s="105" t="s">
@@ -37543,7 +36938,7 @@
         <v>0</v>
       </c>
       <c r="T219" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U219" s="14"/>
       <c r="V219" s="105" t="s">
@@ -37614,7 +37009,7 @@
         <v>0</v>
       </c>
       <c r="T220" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U220" s="14"/>
       <c r="V220" s="105" t="s">
@@ -37685,7 +37080,7 @@
         <v>0</v>
       </c>
       <c r="T221" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U221" s="14"/>
       <c r="V221" s="105" t="s">
@@ -37756,7 +37151,7 @@
         <v>0</v>
       </c>
       <c r="T222" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U222" s="14"/>
       <c r="V222" s="105" t="s">
@@ -37827,7 +37222,7 @@
         <v>0</v>
       </c>
       <c r="T223" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U223" s="14"/>
       <c r="V223" s="105" t="s">
@@ -37898,7 +37293,7 @@
         <v>0</v>
       </c>
       <c r="T224" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U224" s="14" t="s">
         <v>2390</v>
@@ -37968,7 +37363,7 @@
         <v>0</v>
       </c>
       <c r="T225" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U225" s="14" t="s">
         <v>2499</v>
@@ -38041,7 +37436,7 @@
         <v>0</v>
       </c>
       <c r="T226" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U226" s="14" t="s">
         <v>2031</v>
@@ -38114,7 +37509,7 @@
         <v>0</v>
       </c>
       <c r="T227" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U227" s="14" t="s">
         <v>2031</v>
@@ -38187,7 +37582,7 @@
         <v>7267</v>
       </c>
       <c r="T228" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U228" s="14"/>
       <c r="V228" s="108" t="s">
@@ -38255,7 +37650,7 @@
         <v>0</v>
       </c>
       <c r="T229" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U229" s="14" t="s">
         <v>2503</v>
@@ -38328,7 +37723,7 @@
         <v>5090</v>
       </c>
       <c r="T230" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U230" s="14"/>
       <c r="V230" s="105" t="s">
@@ -38399,7 +37794,7 @@
         <v>2933</v>
       </c>
       <c r="T231" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U231" s="13"/>
       <c r="V231" s="105" t="s">
@@ -38470,7 +37865,7 @@
         <v>9249</v>
       </c>
       <c r="T232" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U232" s="14"/>
       <c r="V232" s="105" t="s">
@@ -38541,7 +37936,7 @@
         <v>0</v>
       </c>
       <c r="T233" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U233" s="14"/>
       <c r="V233" s="105" t="s">
@@ -38612,7 +38007,7 @@
         <v>1055</v>
       </c>
       <c r="T234" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U234" s="14" t="s">
         <v>2505</v>
@@ -38685,7 +38080,7 @@
         <v>5382</v>
       </c>
       <c r="T235" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U235" s="14"/>
       <c r="V235" s="105" t="s">
@@ -38756,7 +38151,7 @@
         <v>4905</v>
       </c>
       <c r="T236" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U236" s="14" t="s">
         <v>2169</v>
@@ -38829,7 +38224,7 @@
         <v>5175</v>
       </c>
       <c r="T237" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U237" s="14"/>
       <c r="V237" s="105" t="s">
@@ -38898,7 +38293,7 @@
         <v>0</v>
       </c>
       <c r="T238" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U238" s="14" t="s">
         <v>2149</v>
@@ -38971,7 +38366,7 @@
         <v>4704</v>
       </c>
       <c r="T239" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U239" s="14"/>
       <c r="V239" s="105" t="s">
@@ -39042,7 +38437,7 @@
         <v>5263</v>
       </c>
       <c r="T240" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U240" s="14"/>
       <c r="V240" s="105" t="s">
@@ -39111,7 +38506,7 @@
         <v>0</v>
       </c>
       <c r="T241" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U241" s="14" t="s">
         <v>2410</v>
@@ -39181,7 +38576,7 @@
         <v>0</v>
       </c>
       <c r="T242" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U242" s="14" t="s">
         <v>2410</v>
@@ -39253,7 +38648,7 @@
         <v>114</v>
       </c>
       <c r="T243" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U243" s="14"/>
       <c r="V243" s="108" t="s">
@@ -39324,7 +38719,7 @@
         <v>4094</v>
       </c>
       <c r="T244" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U244" s="14"/>
       <c r="V244" s="105" t="s">
@@ -39395,7 +38790,7 @@
         <v>72</v>
       </c>
       <c r="T245" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U245" s="14"/>
       <c r="V245" s="105" t="s">
@@ -39466,7 +38861,7 @@
         <v>5044</v>
       </c>
       <c r="T246" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U246" s="14"/>
       <c r="V246" s="105" t="s">
@@ -39537,7 +38932,7 @@
         <v>3381</v>
       </c>
       <c r="T247" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U247" s="14"/>
       <c r="V247" s="105" t="s">
@@ -39608,7 +39003,7 @@
         <v>1834</v>
       </c>
       <c r="T248" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U248" s="14"/>
       <c r="V248" s="105" t="s">
@@ -39679,7 +39074,7 @@
         <v>3657</v>
       </c>
       <c r="T249" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U249" s="14"/>
       <c r="V249" s="105" t="s">
@@ -39750,7 +39145,7 @@
         <v>4289</v>
       </c>
       <c r="T250" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U250" s="77" t="s">
         <v>2497</v>
@@ -39823,7 +39218,7 @@
         <v>7124</v>
       </c>
       <c r="T251" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U251" s="14"/>
       <c r="V251" s="105" t="s">
@@ -39892,7 +39287,7 @@
         <v>0</v>
       </c>
       <c r="T252" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U252" s="14" t="s">
         <v>2414</v>
@@ -39965,7 +39360,7 @@
         <v>3925</v>
       </c>
       <c r="T253" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U253" s="14"/>
       <c r="V253" s="105" t="s">
@@ -40036,7 +39431,7 @@
         <v>2342</v>
       </c>
       <c r="T254" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U254" s="14"/>
       <c r="V254" s="105" t="s">
@@ -40107,7 +39502,7 @@
         <v>0</v>
       </c>
       <c r="T255" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U255" s="14"/>
       <c r="V255" s="105" t="s">
@@ -40178,7 +39573,7 @@
         <v>14957</v>
       </c>
       <c r="T256" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U256" s="14"/>
       <c r="V256" s="105" t="s">
@@ -40249,7 +39644,7 @@
         <v>2267</v>
       </c>
       <c r="T257" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U257" s="14"/>
       <c r="V257" s="105" t="s">
@@ -40320,7 +39715,7 @@
         <v>7071</v>
       </c>
       <c r="T258" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U258" s="14"/>
       <c r="V258" s="105" t="s">
@@ -40391,7 +39786,7 @@
         <v>6488</v>
       </c>
       <c r="T259" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U259" s="14"/>
       <c r="V259" s="105" t="s">
@@ -40462,7 +39857,7 @@
         <v>700</v>
       </c>
       <c r="T260" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U260" s="14"/>
       <c r="V260" s="105" t="s">
@@ -40533,7 +39928,7 @@
         <v>485</v>
       </c>
       <c r="T261" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U261" s="14"/>
       <c r="V261" s="105" t="s">
@@ -40604,7 +39999,7 @@
         <v>1149</v>
       </c>
       <c r="T262" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U262" s="14"/>
       <c r="V262" s="105" t="s">
@@ -40675,7 +40070,7 @@
         <v>0</v>
       </c>
       <c r="T263" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U263" s="14"/>
       <c r="V263" s="105" t="s">
@@ -40745,7 +40140,7 @@
         <v>5054</v>
       </c>
       <c r="T264" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U264" s="14"/>
       <c r="V264" s="105" t="s">
@@ -40816,7 +40211,7 @@
         <v>4117</v>
       </c>
       <c r="T265" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U265" s="14"/>
       <c r="V265" s="108" t="s">
@@ -40887,7 +40282,7 @@
         <v>0</v>
       </c>
       <c r="T266" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U266" s="14"/>
       <c r="V266" s="105" t="s">
@@ -40958,7 +40353,7 @@
         <v>0</v>
       </c>
       <c r="T267" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U267" s="14"/>
       <c r="V267" s="105" t="s">
@@ -41029,7 +40424,7 @@
         <v>0</v>
       </c>
       <c r="T268" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U268" s="14"/>
       <c r="V268" s="105" t="s">
@@ -41100,7 +40495,7 @@
         <v>0</v>
       </c>
       <c r="T269" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U269" s="105" t="s">
         <v>2373</v>
@@ -41173,7 +40568,7 @@
         <v>0</v>
       </c>
       <c r="T270" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U270" s="105" t="s">
         <v>2030</v>
@@ -41246,7 +40641,7 @@
         <v>0</v>
       </c>
       <c r="T271" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U271" s="14"/>
       <c r="V271" s="105" t="s">
@@ -41316,7 +40711,7 @@
         <v>0</v>
       </c>
       <c r="T272" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U272" s="14" t="s">
         <v>2213</v>
@@ -41389,7 +40784,7 @@
         <v>10914</v>
       </c>
       <c r="T273" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U273" s="14" t="s">
         <v>2500</v>
@@ -41462,7 +40857,7 @@
         <v>1083</v>
       </c>
       <c r="T274" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U274" s="14" t="s">
         <v>2502</v>
@@ -41535,7 +40930,7 @@
         <v>0</v>
       </c>
       <c r="T275" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U275" s="14" t="s">
         <v>2089</v>
@@ -41608,7 +41003,7 @@
         <v>0</v>
       </c>
       <c r="T276" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U276" s="14" t="s">
         <v>2088</v>
@@ -41681,7 +41076,7 @@
         <v>2443</v>
       </c>
       <c r="T277" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U277" s="14"/>
       <c r="V277" s="105" t="s">
@@ -41752,7 +41147,7 @@
         <v>5427</v>
       </c>
       <c r="T278" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U278" s="14"/>
       <c r="V278" s="105" t="s">
@@ -41823,7 +41218,7 @@
         <v>0</v>
       </c>
       <c r="T279" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U279" s="14"/>
       <c r="V279" s="105" t="s">
@@ -41893,7 +41288,7 @@
         <v>2487</v>
       </c>
       <c r="T280" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U280" s="14"/>
       <c r="V280" s="108" t="s">
@@ -41964,7 +41359,7 @@
         <v>4826</v>
       </c>
       <c r="T281" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U281" s="14"/>
       <c r="V281" s="108" t="s">
@@ -42035,7 +41430,7 @@
         <v>6253</v>
       </c>
       <c r="T282" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U282" s="14"/>
       <c r="V282" s="105" t="s">
@@ -42106,7 +41501,7 @@
         <v>4284</v>
       </c>
       <c r="T283" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U283" s="14"/>
       <c r="V283" s="108" t="s">
@@ -42177,7 +41572,7 @@
         <v>0</v>
       </c>
       <c r="T284" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U284" s="14"/>
       <c r="V284" s="105" t="s">
@@ -42247,7 +41642,7 @@
         <v>0</v>
       </c>
       <c r="T285" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U285" s="14" t="s">
         <v>2451</v>
@@ -42319,7 +41714,7 @@
         <v>5489</v>
       </c>
       <c r="T286" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U286" s="14"/>
       <c r="V286" s="105" t="s">
@@ -42390,7 +41785,7 @@
         <v>1308</v>
       </c>
       <c r="T287" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U287" s="14"/>
       <c r="V287" s="105" t="s">
@@ -42461,7 +41856,7 @@
         <v>747</v>
       </c>
       <c r="T288" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U288" s="14"/>
       <c r="V288" s="105" t="s">
@@ -42532,7 +41927,7 @@
         <v>2368</v>
       </c>
       <c r="T289" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U289" s="14"/>
       <c r="V289" s="105" t="s">
@@ -42603,7 +41998,7 @@
         <v>0</v>
       </c>
       <c r="T290" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U290" s="51" t="s">
         <v>2206</v>
@@ -42676,7 +42071,7 @@
         <v>0</v>
       </c>
       <c r="T291" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U291" s="14" t="s">
         <v>2404</v>
@@ -42749,7 +42144,7 @@
         <v>0</v>
       </c>
       <c r="T292" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U292" s="42" t="s">
         <v>2444</v>
@@ -42821,7 +42216,7 @@
         <v>0</v>
       </c>
       <c r="T293" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U293" s="14" t="s">
         <v>2443</v>
@@ -42894,7 +42289,7 @@
         <v>2486</v>
       </c>
       <c r="T294" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U294" s="14"/>
       <c r="V294" s="105" t="s">
@@ -42965,7 +42360,7 @@
         <v>2580</v>
       </c>
       <c r="T295" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U295" s="14"/>
       <c r="V295" s="105" t="s">
@@ -43036,7 +42431,7 @@
         <v>3503</v>
       </c>
       <c r="T296" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U296" s="14"/>
       <c r="V296" s="105" t="s">
@@ -43107,7 +42502,7 @@
         <v>826</v>
       </c>
       <c r="T297" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U297" s="14" t="s">
         <v>2487</v>
@@ -43179,7 +42574,7 @@
         <v>1972</v>
       </c>
       <c r="T298" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U298" s="14"/>
       <c r="V298" s="105" t="s">
@@ -43250,7 +42645,7 @@
         <v>0</v>
       </c>
       <c r="T299" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U299" s="57"/>
       <c r="V299" s="105" t="s">
@@ -43321,7 +42716,7 @@
         <v>0</v>
       </c>
       <c r="T300" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U300" s="14" t="s">
         <v>2428</v>
@@ -43394,7 +42789,7 @@
         <v>6808</v>
       </c>
       <c r="T301" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U301" s="14"/>
       <c r="V301" s="105" t="s">
@@ -43465,7 +42860,7 @@
         <v>22</v>
       </c>
       <c r="T302" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U302" s="14"/>
       <c r="V302" s="105" t="s">
@@ -43534,7 +42929,7 @@
         <v>0</v>
       </c>
       <c r="T303" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U303" s="14" t="s">
         <v>2453</v>
@@ -43606,7 +43001,7 @@
         <v>7791</v>
       </c>
       <c r="T304" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U304" s="14"/>
       <c r="V304" s="105" t="s">
@@ -43677,7 +43072,7 @@
         <v>0</v>
       </c>
       <c r="T305" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U305" s="14"/>
       <c r="V305" s="105" t="s">
@@ -43747,7 +43142,7 @@
         <v>4055</v>
       </c>
       <c r="T306" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U306" s="14" t="s">
         <v>2507</v>
@@ -43820,7 +43215,7 @@
         <v>6597</v>
       </c>
       <c r="T307" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U307" s="8"/>
       <c r="V307" s="105" t="s">
@@ -43891,7 +43286,7 @@
         <v>0</v>
       </c>
       <c r="T308" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U308" s="14"/>
       <c r="V308" s="105" t="s">
@@ -43961,7 +43356,7 @@
         <v>2179</v>
       </c>
       <c r="T309" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U309" s="14"/>
       <c r="V309" s="105" t="s">
@@ -44032,7 +43427,7 @@
         <v>0</v>
       </c>
       <c r="T310" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U310" s="14"/>
       <c r="V310" s="105" t="s">
@@ -44102,7 +43497,7 @@
         <v>2983</v>
       </c>
       <c r="T311" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U311" s="14"/>
       <c r="V311" s="105" t="s">
@@ -44173,7 +43568,7 @@
         <v>0</v>
       </c>
       <c r="T312" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U312" s="14"/>
       <c r="V312" s="105" t="s">
@@ -44244,7 +43639,7 @@
         <v>0</v>
       </c>
       <c r="T313" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U313" s="14"/>
       <c r="V313" s="105" t="s">
@@ -44315,7 +43710,7 @@
         <v>5087</v>
       </c>
       <c r="T314" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U314" s="14"/>
       <c r="V314" s="105" t="s">
@@ -44386,7 +43781,7 @@
         <v>0</v>
       </c>
       <c r="T315" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U315" s="8"/>
       <c r="V315" s="105" t="s">
@@ -44457,7 +43852,7 @@
         <v>2</v>
       </c>
       <c r="T316" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U316" s="54"/>
       <c r="V316" s="105" t="s">
@@ -44528,7 +43923,7 @@
         <v>0</v>
       </c>
       <c r="T317" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U317" s="14"/>
       <c r="V317" s="105" t="s">
@@ -44599,7 +43994,7 @@
         <v>0</v>
       </c>
       <c r="T318" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U318" s="14" t="s">
         <v>2454</v>
@@ -44672,7 +44067,7 @@
         <v>2610</v>
       </c>
       <c r="T319" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U319" s="14"/>
       <c r="V319" s="105" t="s">
@@ -44742,7 +44137,7 @@
         <v>7147</v>
       </c>
       <c r="T320" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U320" s="14"/>
       <c r="V320" s="105" t="s">
@@ -44813,7 +44208,7 @@
         <v>9920</v>
       </c>
       <c r="T321" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U321" s="14"/>
       <c r="V321" s="108" t="s">
@@ -44884,7 +44279,7 @@
         <v>2067</v>
       </c>
       <c r="T322" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U322" s="14"/>
       <c r="V322" s="108" t="s">
@@ -44955,7 +44350,7 @@
         <v>7127</v>
       </c>
       <c r="T323" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U323" s="59"/>
       <c r="V323" s="105" t="s">
@@ -45026,7 +44421,7 @@
         <v>4207</v>
       </c>
       <c r="T324" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U324" s="14"/>
       <c r="V324" s="108" t="s">
@@ -45097,7 +44492,7 @@
         <v>1830</v>
       </c>
       <c r="T325" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U325" s="14"/>
       <c r="V325" s="108" t="s">
@@ -45168,7 +44563,7 @@
         <v>7523</v>
       </c>
       <c r="T326" s="89">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="U326" s="14"/>
       <c r="V326" s="105" t="s">
@@ -45190,135 +44585,135 @@
     <sortCondition ref="B2:B438"/>
   </sortState>
   <conditionalFormatting sqref="F208">
-    <cfRule type="duplicateValues" dxfId="782" priority="1661"/>
-    <cfRule type="duplicateValues" dxfId="781" priority="1662"/>
+    <cfRule type="duplicateValues" dxfId="727" priority="1661"/>
+    <cfRule type="duplicateValues" dxfId="726" priority="1662"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F208">
-    <cfRule type="duplicateValues" dxfId="780" priority="1663"/>
+    <cfRule type="duplicateValues" dxfId="725" priority="1663"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F97">
-    <cfRule type="duplicateValues" dxfId="779" priority="1655"/>
-    <cfRule type="duplicateValues" dxfId="778" priority="1656"/>
+    <cfRule type="duplicateValues" dxfId="724" priority="1655"/>
+    <cfRule type="duplicateValues" dxfId="723" priority="1656"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F97">
-    <cfRule type="duplicateValues" dxfId="777" priority="1657"/>
+    <cfRule type="duplicateValues" dxfId="722" priority="1657"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:T326">
-    <cfRule type="cellIs" dxfId="776" priority="1654" operator="equal">
+    <cfRule type="cellIs" dxfId="721" priority="1654" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F132">
-    <cfRule type="duplicateValues" dxfId="775" priority="1640"/>
-    <cfRule type="duplicateValues" dxfId="774" priority="1641"/>
+    <cfRule type="duplicateValues" dxfId="720" priority="1640"/>
+    <cfRule type="duplicateValues" dxfId="719" priority="1641"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F132">
-    <cfRule type="duplicateValues" dxfId="773" priority="1642"/>
+    <cfRule type="duplicateValues" dxfId="718" priority="1642"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F28">
-    <cfRule type="duplicateValues" dxfId="772" priority="1635"/>
-    <cfRule type="duplicateValues" dxfId="771" priority="1636"/>
+    <cfRule type="duplicateValues" dxfId="717" priority="1635"/>
+    <cfRule type="duplicateValues" dxfId="716" priority="1636"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F28">
-    <cfRule type="duplicateValues" dxfId="770" priority="1637"/>
+    <cfRule type="duplicateValues" dxfId="715" priority="1637"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F302">
-    <cfRule type="duplicateValues" dxfId="769" priority="1625"/>
-    <cfRule type="duplicateValues" dxfId="768" priority="1626"/>
+    <cfRule type="duplicateValues" dxfId="714" priority="1625"/>
+    <cfRule type="duplicateValues" dxfId="713" priority="1626"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F302">
-    <cfRule type="duplicateValues" dxfId="767" priority="1627"/>
+    <cfRule type="duplicateValues" dxfId="712" priority="1627"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F183">
-    <cfRule type="duplicateValues" dxfId="766" priority="1581"/>
-    <cfRule type="duplicateValues" dxfId="765" priority="1582"/>
+    <cfRule type="duplicateValues" dxfId="711" priority="1581"/>
+    <cfRule type="duplicateValues" dxfId="710" priority="1582"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F183">
-    <cfRule type="duplicateValues" dxfId="764" priority="1583"/>
+    <cfRule type="duplicateValues" dxfId="709" priority="1583"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F186">
-    <cfRule type="duplicateValues" dxfId="763" priority="1577"/>
-    <cfRule type="duplicateValues" dxfId="762" priority="1578"/>
+    <cfRule type="duplicateValues" dxfId="708" priority="1577"/>
+    <cfRule type="duplicateValues" dxfId="707" priority="1578"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F186">
-    <cfRule type="duplicateValues" dxfId="761" priority="1579"/>
+    <cfRule type="duplicateValues" dxfId="706" priority="1579"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F323">
-    <cfRule type="duplicateValues" dxfId="760" priority="1479"/>
+    <cfRule type="duplicateValues" dxfId="705" priority="1479"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F323">
-    <cfRule type="duplicateValues" dxfId="759" priority="1476"/>
+    <cfRule type="duplicateValues" dxfId="704" priority="1476"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F323">
-    <cfRule type="duplicateValues" dxfId="758" priority="1477"/>
-    <cfRule type="duplicateValues" dxfId="757" priority="1478"/>
+    <cfRule type="duplicateValues" dxfId="703" priority="1477"/>
+    <cfRule type="duplicateValues" dxfId="702" priority="1478"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F263">
-    <cfRule type="duplicateValues" dxfId="756" priority="1464"/>
+    <cfRule type="duplicateValues" dxfId="701" priority="1464"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F263">
-    <cfRule type="duplicateValues" dxfId="755" priority="1465"/>
-    <cfRule type="duplicateValues" dxfId="754" priority="1466"/>
+    <cfRule type="duplicateValues" dxfId="700" priority="1465"/>
+    <cfRule type="duplicateValues" dxfId="699" priority="1466"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="753" priority="1100"/>
+    <cfRule type="duplicateValues" dxfId="698" priority="1100"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F324">
-    <cfRule type="duplicateValues" dxfId="752" priority="397"/>
+    <cfRule type="duplicateValues" dxfId="697" priority="397"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F324">
-    <cfRule type="duplicateValues" dxfId="751" priority="394"/>
+    <cfRule type="duplicateValues" dxfId="696" priority="394"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F324">
-    <cfRule type="duplicateValues" dxfId="750" priority="395"/>
-    <cfRule type="duplicateValues" dxfId="749" priority="396"/>
+    <cfRule type="duplicateValues" dxfId="695" priority="395"/>
+    <cfRule type="duplicateValues" dxfId="694" priority="396"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F325:F326">
-    <cfRule type="duplicateValues" dxfId="748" priority="391"/>
+    <cfRule type="duplicateValues" dxfId="693" priority="391"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F325:F326">
-    <cfRule type="duplicateValues" dxfId="747" priority="388"/>
+    <cfRule type="duplicateValues" dxfId="692" priority="388"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F325:F326">
-    <cfRule type="duplicateValues" dxfId="746" priority="389"/>
-    <cfRule type="duplicateValues" dxfId="745" priority="390"/>
+    <cfRule type="duplicateValues" dxfId="691" priority="389"/>
+    <cfRule type="duplicateValues" dxfId="690" priority="390"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F188">
-    <cfRule type="duplicateValues" dxfId="744" priority="178"/>
-    <cfRule type="duplicateValues" dxfId="743" priority="179"/>
+    <cfRule type="duplicateValues" dxfId="689" priority="178"/>
+    <cfRule type="duplicateValues" dxfId="688" priority="179"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F188">
-    <cfRule type="duplicateValues" dxfId="742" priority="180"/>
+    <cfRule type="duplicateValues" dxfId="687" priority="180"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F188">
-    <cfRule type="duplicateValues" dxfId="741" priority="181"/>
+    <cfRule type="duplicateValues" dxfId="686" priority="181"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F303:F322 F218:F230 F2:F3 F184:F185 F187 F209:F216 F264:F301 F232:F262 F10:F27 F133:F182 F29:F51 F189:F207 F98:F131 F53:F96">
-    <cfRule type="duplicateValues" dxfId="740" priority="1895"/>
-    <cfRule type="duplicateValues" dxfId="739" priority="1896"/>
+    <cfRule type="duplicateValues" dxfId="685" priority="1895"/>
+    <cfRule type="duplicateValues" dxfId="684" priority="1896"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F303:F322 F218:F230 F2:F3 F184:F185 F187 F209:F216 F264:F301 F232:F262 F10:F27 F133:F182 F29:F51 F189:F207 F98:F131 F53:F96">
-    <cfRule type="duplicateValues" dxfId="738" priority="1925"/>
+    <cfRule type="duplicateValues" dxfId="683" priority="1925"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F52">
-    <cfRule type="duplicateValues" dxfId="737" priority="73"/>
-    <cfRule type="duplicateValues" dxfId="736" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="682" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="681" priority="74"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F52">
-    <cfRule type="duplicateValues" dxfId="735" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="680" priority="75"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F52">
-    <cfRule type="duplicateValues" dxfId="734" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="679" priority="76"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F264:F322 F184:F185 F2:F3 F232:F262 F187 F10:F51 F189:F230 F53:F182">
-    <cfRule type="duplicateValues" dxfId="733" priority="1988"/>
+    <cfRule type="duplicateValues" dxfId="678" priority="1988"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4:F9">
-    <cfRule type="duplicateValues" dxfId="732" priority="1991"/>
+    <cfRule type="duplicateValues" dxfId="677" priority="1991"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4:F9">
-    <cfRule type="duplicateValues" dxfId="731" priority="1993"/>
-    <cfRule type="duplicateValues" dxfId="730" priority="1994"/>
+    <cfRule type="duplicateValues" dxfId="676" priority="1993"/>
+    <cfRule type="duplicateValues" dxfId="675" priority="1994"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -48317,110 +47712,110 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4:A7">
-    <cfRule type="duplicateValues" dxfId="729" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="674" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A4:A7">
-    <cfRule type="duplicateValues" dxfId="728" priority="39"/>
-    <cfRule type="duplicateValues" dxfId="727" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="673" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="672" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" dxfId="726" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="671" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A230:A245 A208:A228 A176:A206 A165:A174 A156:A163 A148:A149 A151:A154 A110:A146 A29:A108 A8:A27 A2:A3">
-    <cfRule type="duplicateValues" dxfId="725" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="724" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="670" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="669" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A230:A245 A208:A228 A176:A206 A165:A174 A156:A163 A148:A149 A151:A154 A110:A146 A29:A108 A8:A27 A2:A3">
-    <cfRule type="duplicateValues" dxfId="723" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="668" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A208:A245 A176:A206 A156:A174 A148:A149 A151:A154 A8:A146 A2:A3">
-    <cfRule type="duplicateValues" dxfId="722" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="667" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A28">
-    <cfRule type="duplicateValues" dxfId="721" priority="34"/>
-    <cfRule type="duplicateValues" dxfId="720" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="666" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="665" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A28">
-    <cfRule type="duplicateValues" dxfId="719" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="664" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A109">
-    <cfRule type="duplicateValues" dxfId="718" priority="31"/>
-    <cfRule type="duplicateValues" dxfId="717" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="663" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="662" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A109">
-    <cfRule type="duplicateValues" dxfId="716" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="661" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A147">
-    <cfRule type="duplicateValues" dxfId="715" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="714" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="660" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="659" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A147">
-    <cfRule type="duplicateValues" dxfId="713" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="658" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A150">
-    <cfRule type="duplicateValues" dxfId="712" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="711" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="657" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="656" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A150">
-    <cfRule type="duplicateValues" dxfId="710" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="655" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A155">
-    <cfRule type="duplicateValues" dxfId="709" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="654" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A155">
-    <cfRule type="duplicateValues" dxfId="708" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="707" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="653" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="652" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A164">
-    <cfRule type="duplicateValues" dxfId="706" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="705" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="651" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="650" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A164">
-    <cfRule type="duplicateValues" dxfId="704" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="649" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A207">
-    <cfRule type="duplicateValues" dxfId="703" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="648" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A207">
-    <cfRule type="duplicateValues" dxfId="702" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="701" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="647" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="646" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A229">
-    <cfRule type="duplicateValues" dxfId="700" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="699" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="645" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="644" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A229">
-    <cfRule type="duplicateValues" dxfId="698" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="643" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A246">
-    <cfRule type="duplicateValues" dxfId="697" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="642" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A246">
-    <cfRule type="duplicateValues" dxfId="696" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="641" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A246">
-    <cfRule type="duplicateValues" dxfId="695" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="694" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="640" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="639" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A247">
-    <cfRule type="duplicateValues" dxfId="693" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="638" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A247">
-    <cfRule type="duplicateValues" dxfId="692" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="637" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A247">
-    <cfRule type="duplicateValues" dxfId="691" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="690" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="636" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="635" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A248:A249">
-    <cfRule type="duplicateValues" dxfId="689" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="634" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A248:A249">
-    <cfRule type="duplicateValues" dxfId="688" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="633" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A248:A249">
-    <cfRule type="duplicateValues" dxfId="687" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="686" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="632" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="631" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -50735,7 +50130,7 @@
     </filterColumn>
   </autoFilter>
   <conditionalFormatting sqref="B135">
-    <cfRule type="duplicateValues" dxfId="685" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="630" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -52553,7 +51948,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A361">
-    <cfRule type="cellIs" dxfId="684" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="629" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -67716,6 +67111,16 @@
   </sheetData>
   <autoFilter ref="A1:DF144"/>
   <mergeCells count="26">
+    <mergeCell ref="J167:N167"/>
+    <mergeCell ref="I142:M142"/>
+    <mergeCell ref="I143:M143"/>
+    <mergeCell ref="I141:M141"/>
+    <mergeCell ref="I144:M144"/>
+    <mergeCell ref="I131:M131"/>
+    <mergeCell ref="I132:M132"/>
+    <mergeCell ref="I133:M133"/>
+    <mergeCell ref="I134:M134"/>
+    <mergeCell ref="I135:M135"/>
     <mergeCell ref="I140:M140"/>
     <mergeCell ref="I139:M139"/>
     <mergeCell ref="I137:M137"/>
@@ -67732,407 +67137,397 @@
     <mergeCell ref="I130:M130"/>
     <mergeCell ref="I127:M127"/>
     <mergeCell ref="I136:M136"/>
-    <mergeCell ref="I131:M131"/>
-    <mergeCell ref="I132:M132"/>
-    <mergeCell ref="I133:M133"/>
-    <mergeCell ref="I134:M134"/>
-    <mergeCell ref="I135:M135"/>
-    <mergeCell ref="J167:N167"/>
-    <mergeCell ref="I142:M142"/>
-    <mergeCell ref="I143:M143"/>
-    <mergeCell ref="I141:M141"/>
-    <mergeCell ref="I144:M144"/>
   </mergeCells>
   <conditionalFormatting sqref="F100:G100">
-    <cfRule type="duplicateValues" dxfId="683" priority="320"/>
-    <cfRule type="duplicateValues" dxfId="682" priority="321"/>
+    <cfRule type="duplicateValues" dxfId="628" priority="320"/>
+    <cfRule type="duplicateValues" dxfId="627" priority="321"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F102:G102">
-    <cfRule type="duplicateValues" dxfId="681" priority="317"/>
-    <cfRule type="duplicateValues" dxfId="680" priority="318"/>
+    <cfRule type="duplicateValues" dxfId="626" priority="317"/>
+    <cfRule type="duplicateValues" dxfId="625" priority="318"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F102">
-    <cfRule type="duplicateValues" dxfId="679" priority="319"/>
+    <cfRule type="duplicateValues" dxfId="624" priority="319"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F103:G103">
-    <cfRule type="duplicateValues" dxfId="678" priority="314"/>
-    <cfRule type="duplicateValues" dxfId="677" priority="315"/>
+    <cfRule type="duplicateValues" dxfId="623" priority="314"/>
+    <cfRule type="duplicateValues" dxfId="622" priority="315"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F103">
-    <cfRule type="duplicateValues" dxfId="676" priority="316"/>
+    <cfRule type="duplicateValues" dxfId="621" priority="316"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F105:G105">
-    <cfRule type="duplicateValues" dxfId="675" priority="311"/>
-    <cfRule type="duplicateValues" dxfId="674" priority="312"/>
+    <cfRule type="duplicateValues" dxfId="620" priority="311"/>
+    <cfRule type="duplicateValues" dxfId="619" priority="312"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F105">
-    <cfRule type="duplicateValues" dxfId="673" priority="313"/>
+    <cfRule type="duplicateValues" dxfId="618" priority="313"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F106:G106">
-    <cfRule type="duplicateValues" dxfId="672" priority="308"/>
-    <cfRule type="duplicateValues" dxfId="671" priority="309"/>
+    <cfRule type="duplicateValues" dxfId="617" priority="308"/>
+    <cfRule type="duplicateValues" dxfId="616" priority="309"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F106">
-    <cfRule type="duplicateValues" dxfId="670" priority="310"/>
+    <cfRule type="duplicateValues" dxfId="615" priority="310"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F108:G108">
-    <cfRule type="duplicateValues" dxfId="669" priority="305"/>
-    <cfRule type="duplicateValues" dxfId="668" priority="306"/>
+    <cfRule type="duplicateValues" dxfId="614" priority="305"/>
+    <cfRule type="duplicateValues" dxfId="613" priority="306"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F108">
-    <cfRule type="duplicateValues" dxfId="667" priority="307"/>
+    <cfRule type="duplicateValues" dxfId="612" priority="307"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F109:G109">
-    <cfRule type="duplicateValues" dxfId="666" priority="302"/>
-    <cfRule type="duplicateValues" dxfId="665" priority="303"/>
+    <cfRule type="duplicateValues" dxfId="611" priority="302"/>
+    <cfRule type="duplicateValues" dxfId="610" priority="303"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F109">
-    <cfRule type="duplicateValues" dxfId="664" priority="304"/>
+    <cfRule type="duplicateValues" dxfId="609" priority="304"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F110:G110">
-    <cfRule type="duplicateValues" dxfId="663" priority="299"/>
-    <cfRule type="duplicateValues" dxfId="662" priority="300"/>
+    <cfRule type="duplicateValues" dxfId="608" priority="299"/>
+    <cfRule type="duplicateValues" dxfId="607" priority="300"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F110">
-    <cfRule type="duplicateValues" dxfId="661" priority="301"/>
+    <cfRule type="duplicateValues" dxfId="606" priority="301"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F112:G112">
-    <cfRule type="duplicateValues" dxfId="660" priority="296"/>
-    <cfRule type="duplicateValues" dxfId="659" priority="297"/>
+    <cfRule type="duplicateValues" dxfId="605" priority="296"/>
+    <cfRule type="duplicateValues" dxfId="604" priority="297"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F112">
-    <cfRule type="duplicateValues" dxfId="658" priority="298"/>
+    <cfRule type="duplicateValues" dxfId="603" priority="298"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F113:G113">
-    <cfRule type="duplicateValues" dxfId="657" priority="293"/>
-    <cfRule type="duplicateValues" dxfId="656" priority="294"/>
+    <cfRule type="duplicateValues" dxfId="602" priority="293"/>
+    <cfRule type="duplicateValues" dxfId="601" priority="294"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F113">
-    <cfRule type="duplicateValues" dxfId="655" priority="295"/>
+    <cfRule type="duplicateValues" dxfId="600" priority="295"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F114:G114">
-    <cfRule type="duplicateValues" dxfId="654" priority="290"/>
-    <cfRule type="duplicateValues" dxfId="653" priority="291"/>
+    <cfRule type="duplicateValues" dxfId="599" priority="290"/>
+    <cfRule type="duplicateValues" dxfId="598" priority="291"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F114">
-    <cfRule type="duplicateValues" dxfId="652" priority="292"/>
+    <cfRule type="duplicateValues" dxfId="597" priority="292"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F115:G115">
-    <cfRule type="duplicateValues" dxfId="651" priority="287"/>
-    <cfRule type="duplicateValues" dxfId="650" priority="288"/>
+    <cfRule type="duplicateValues" dxfId="596" priority="287"/>
+    <cfRule type="duplicateValues" dxfId="595" priority="288"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F115">
-    <cfRule type="duplicateValues" dxfId="649" priority="289"/>
+    <cfRule type="duplicateValues" dxfId="594" priority="289"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F116:G116">
-    <cfRule type="duplicateValues" dxfId="648" priority="284"/>
-    <cfRule type="duplicateValues" dxfId="647" priority="285"/>
+    <cfRule type="duplicateValues" dxfId="593" priority="284"/>
+    <cfRule type="duplicateValues" dxfId="592" priority="285"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F116">
-    <cfRule type="duplicateValues" dxfId="646" priority="286"/>
+    <cfRule type="duplicateValues" dxfId="591" priority="286"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F117:G117">
-    <cfRule type="duplicateValues" dxfId="645" priority="281"/>
-    <cfRule type="duplicateValues" dxfId="644" priority="282"/>
+    <cfRule type="duplicateValues" dxfId="590" priority="281"/>
+    <cfRule type="duplicateValues" dxfId="589" priority="282"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F117">
-    <cfRule type="duplicateValues" dxfId="643" priority="283"/>
+    <cfRule type="duplicateValues" dxfId="588" priority="283"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F118:G118">
-    <cfRule type="duplicateValues" dxfId="642" priority="278"/>
-    <cfRule type="duplicateValues" dxfId="641" priority="279"/>
+    <cfRule type="duplicateValues" dxfId="587" priority="278"/>
+    <cfRule type="duplicateValues" dxfId="586" priority="279"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F118">
-    <cfRule type="duplicateValues" dxfId="640" priority="280"/>
+    <cfRule type="duplicateValues" dxfId="585" priority="280"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F119:G119">
-    <cfRule type="duplicateValues" dxfId="639" priority="275"/>
-    <cfRule type="duplicateValues" dxfId="638" priority="276"/>
+    <cfRule type="duplicateValues" dxfId="584" priority="275"/>
+    <cfRule type="duplicateValues" dxfId="583" priority="276"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F119">
-    <cfRule type="duplicateValues" dxfId="637" priority="277"/>
+    <cfRule type="duplicateValues" dxfId="582" priority="277"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F120:G120">
-    <cfRule type="duplicateValues" dxfId="636" priority="272"/>
-    <cfRule type="duplicateValues" dxfId="635" priority="273"/>
+    <cfRule type="duplicateValues" dxfId="581" priority="272"/>
+    <cfRule type="duplicateValues" dxfId="580" priority="273"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F120">
-    <cfRule type="duplicateValues" dxfId="634" priority="274"/>
+    <cfRule type="duplicateValues" dxfId="579" priority="274"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F121:G121">
-    <cfRule type="duplicateValues" dxfId="633" priority="269"/>
-    <cfRule type="duplicateValues" dxfId="632" priority="270"/>
+    <cfRule type="duplicateValues" dxfId="578" priority="269"/>
+    <cfRule type="duplicateValues" dxfId="577" priority="270"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F121">
-    <cfRule type="duplicateValues" dxfId="631" priority="271"/>
+    <cfRule type="duplicateValues" dxfId="576" priority="271"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F122:G122">
-    <cfRule type="duplicateValues" dxfId="630" priority="266"/>
-    <cfRule type="duplicateValues" dxfId="629" priority="267"/>
+    <cfRule type="duplicateValues" dxfId="575" priority="266"/>
+    <cfRule type="duplicateValues" dxfId="574" priority="267"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F122">
-    <cfRule type="duplicateValues" dxfId="628" priority="268"/>
+    <cfRule type="duplicateValues" dxfId="573" priority="268"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F124:G124">
-    <cfRule type="duplicateValues" dxfId="627" priority="263"/>
-    <cfRule type="duplicateValues" dxfId="626" priority="264"/>
+    <cfRule type="duplicateValues" dxfId="572" priority="263"/>
+    <cfRule type="duplicateValues" dxfId="571" priority="264"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F124">
-    <cfRule type="duplicateValues" dxfId="625" priority="265"/>
+    <cfRule type="duplicateValues" dxfId="570" priority="265"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H126 H144">
-    <cfRule type="cellIs" dxfId="624" priority="257" operator="equal">
+    <cfRule type="cellIs" dxfId="569" priority="257" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G126">
-    <cfRule type="duplicateValues" dxfId="623" priority="258"/>
-    <cfRule type="duplicateValues" dxfId="622" priority="259"/>
+    <cfRule type="duplicateValues" dxfId="568" priority="258"/>
+    <cfRule type="duplicateValues" dxfId="567" priority="259"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F126">
-    <cfRule type="duplicateValues" dxfId="621" priority="260"/>
-    <cfRule type="duplicateValues" dxfId="620" priority="261"/>
+    <cfRule type="duplicateValues" dxfId="566" priority="260"/>
+    <cfRule type="duplicateValues" dxfId="565" priority="261"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F126">
-    <cfRule type="duplicateValues" dxfId="619" priority="262"/>
+    <cfRule type="duplicateValues" dxfId="564" priority="262"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H128">
-    <cfRule type="cellIs" dxfId="618" priority="247" operator="equal">
+    <cfRule type="cellIs" dxfId="563" priority="247" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G128">
-    <cfRule type="duplicateValues" dxfId="617" priority="248"/>
-    <cfRule type="duplicateValues" dxfId="616" priority="249"/>
+    <cfRule type="duplicateValues" dxfId="562" priority="248"/>
+    <cfRule type="duplicateValues" dxfId="561" priority="249"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F128">
-    <cfRule type="duplicateValues" dxfId="615" priority="250"/>
-    <cfRule type="duplicateValues" dxfId="614" priority="251"/>
+    <cfRule type="duplicateValues" dxfId="560" priority="250"/>
+    <cfRule type="duplicateValues" dxfId="559" priority="251"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F128">
-    <cfRule type="duplicateValues" dxfId="613" priority="252"/>
+    <cfRule type="duplicateValues" dxfId="558" priority="252"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H129:H130">
-    <cfRule type="cellIs" dxfId="612" priority="237" operator="equal">
+    <cfRule type="cellIs" dxfId="557" priority="237" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G129:G130">
-    <cfRule type="duplicateValues" dxfId="611" priority="238"/>
-    <cfRule type="duplicateValues" dxfId="610" priority="239"/>
+    <cfRule type="duplicateValues" dxfId="556" priority="238"/>
+    <cfRule type="duplicateValues" dxfId="555" priority="239"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F129:F130">
-    <cfRule type="duplicateValues" dxfId="609" priority="240"/>
-    <cfRule type="duplicateValues" dxfId="608" priority="241"/>
+    <cfRule type="duplicateValues" dxfId="554" priority="240"/>
+    <cfRule type="duplicateValues" dxfId="553" priority="241"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F129:F130">
-    <cfRule type="duplicateValues" dxfId="607" priority="242"/>
+    <cfRule type="duplicateValues" dxfId="552" priority="242"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H131">
-    <cfRule type="cellIs" dxfId="606" priority="227" operator="equal">
+    <cfRule type="cellIs" dxfId="551" priority="227" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G131">
-    <cfRule type="duplicateValues" dxfId="605" priority="228"/>
-    <cfRule type="duplicateValues" dxfId="604" priority="229"/>
+    <cfRule type="duplicateValues" dxfId="550" priority="228"/>
+    <cfRule type="duplicateValues" dxfId="549" priority="229"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F131">
-    <cfRule type="duplicateValues" dxfId="603" priority="230"/>
-    <cfRule type="duplicateValues" dxfId="602" priority="231"/>
+    <cfRule type="duplicateValues" dxfId="548" priority="230"/>
+    <cfRule type="duplicateValues" dxfId="547" priority="231"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F131">
-    <cfRule type="duplicateValues" dxfId="601" priority="232"/>
+    <cfRule type="duplicateValues" dxfId="546" priority="232"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H132:H133">
-    <cfRule type="cellIs" dxfId="600" priority="217" operator="equal">
+    <cfRule type="cellIs" dxfId="545" priority="217" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G132:G133">
-    <cfRule type="duplicateValues" dxfId="599" priority="218"/>
-    <cfRule type="duplicateValues" dxfId="598" priority="219"/>
+    <cfRule type="duplicateValues" dxfId="544" priority="218"/>
+    <cfRule type="duplicateValues" dxfId="543" priority="219"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F132:F133">
-    <cfRule type="duplicateValues" dxfId="597" priority="220"/>
-    <cfRule type="duplicateValues" dxfId="596" priority="221"/>
+    <cfRule type="duplicateValues" dxfId="542" priority="220"/>
+    <cfRule type="duplicateValues" dxfId="541" priority="221"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F132:F133">
-    <cfRule type="duplicateValues" dxfId="595" priority="222"/>
+    <cfRule type="duplicateValues" dxfId="540" priority="222"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H134">
-    <cfRule type="cellIs" dxfId="594" priority="207" operator="equal">
+    <cfRule type="cellIs" dxfId="539" priority="207" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G134">
-    <cfRule type="duplicateValues" dxfId="593" priority="208"/>
-    <cfRule type="duplicateValues" dxfId="592" priority="209"/>
+    <cfRule type="duplicateValues" dxfId="538" priority="208"/>
+    <cfRule type="duplicateValues" dxfId="537" priority="209"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F134">
-    <cfRule type="duplicateValues" dxfId="591" priority="210"/>
-    <cfRule type="duplicateValues" dxfId="590" priority="211"/>
+    <cfRule type="duplicateValues" dxfId="536" priority="210"/>
+    <cfRule type="duplicateValues" dxfId="535" priority="211"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F134">
-    <cfRule type="duplicateValues" dxfId="589" priority="212"/>
+    <cfRule type="duplicateValues" dxfId="534" priority="212"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H135:H136">
-    <cfRule type="cellIs" dxfId="588" priority="197" operator="equal">
+    <cfRule type="cellIs" dxfId="533" priority="197" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G135:G136">
-    <cfRule type="duplicateValues" dxfId="587" priority="198"/>
-    <cfRule type="duplicateValues" dxfId="586" priority="199"/>
+    <cfRule type="duplicateValues" dxfId="532" priority="198"/>
+    <cfRule type="duplicateValues" dxfId="531" priority="199"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F135:F136">
-    <cfRule type="duplicateValues" dxfId="585" priority="200"/>
-    <cfRule type="duplicateValues" dxfId="584" priority="201"/>
+    <cfRule type="duplicateValues" dxfId="530" priority="200"/>
+    <cfRule type="duplicateValues" dxfId="529" priority="201"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F135:F136">
-    <cfRule type="duplicateValues" dxfId="583" priority="202"/>
+    <cfRule type="duplicateValues" dxfId="528" priority="202"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H137">
-    <cfRule type="cellIs" dxfId="582" priority="187" operator="equal">
+    <cfRule type="cellIs" dxfId="527" priority="187" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H138">
-    <cfRule type="cellIs" dxfId="581" priority="177" operator="equal">
+    <cfRule type="cellIs" dxfId="526" priority="177" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G138">
-    <cfRule type="duplicateValues" dxfId="580" priority="178"/>
-    <cfRule type="duplicateValues" dxfId="579" priority="179"/>
+    <cfRule type="duplicateValues" dxfId="525" priority="178"/>
+    <cfRule type="duplicateValues" dxfId="524" priority="179"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F138">
-    <cfRule type="duplicateValues" dxfId="578" priority="180"/>
-    <cfRule type="duplicateValues" dxfId="577" priority="181"/>
+    <cfRule type="duplicateValues" dxfId="523" priority="180"/>
+    <cfRule type="duplicateValues" dxfId="522" priority="181"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F138">
-    <cfRule type="duplicateValues" dxfId="576" priority="182"/>
+    <cfRule type="duplicateValues" dxfId="521" priority="182"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H127">
-    <cfRule type="cellIs" dxfId="575" priority="167" operator="equal">
+    <cfRule type="cellIs" dxfId="520" priority="167" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G127">
-    <cfRule type="duplicateValues" dxfId="574" priority="168"/>
-    <cfRule type="duplicateValues" dxfId="573" priority="169"/>
+    <cfRule type="duplicateValues" dxfId="519" priority="168"/>
+    <cfRule type="duplicateValues" dxfId="518" priority="169"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F127">
-    <cfRule type="duplicateValues" dxfId="572" priority="170"/>
-    <cfRule type="duplicateValues" dxfId="571" priority="171"/>
+    <cfRule type="duplicateValues" dxfId="517" priority="170"/>
+    <cfRule type="duplicateValues" dxfId="516" priority="171"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F127">
-    <cfRule type="duplicateValues" dxfId="570" priority="172"/>
+    <cfRule type="duplicateValues" dxfId="515" priority="172"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H139">
-    <cfRule type="cellIs" dxfId="569" priority="157" operator="equal">
+    <cfRule type="cellIs" dxfId="514" priority="157" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G139">
-    <cfRule type="duplicateValues" dxfId="568" priority="158"/>
-    <cfRule type="duplicateValues" dxfId="567" priority="159"/>
+    <cfRule type="duplicateValues" dxfId="513" priority="158"/>
+    <cfRule type="duplicateValues" dxfId="512" priority="159"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F139">
-    <cfRule type="duplicateValues" dxfId="566" priority="160"/>
-    <cfRule type="duplicateValues" dxfId="565" priority="161"/>
+    <cfRule type="duplicateValues" dxfId="511" priority="160"/>
+    <cfRule type="duplicateValues" dxfId="510" priority="161"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F139">
-    <cfRule type="duplicateValues" dxfId="564" priority="162"/>
+    <cfRule type="duplicateValues" dxfId="509" priority="162"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G140">
-    <cfRule type="duplicateValues" dxfId="563" priority="152"/>
-    <cfRule type="duplicateValues" dxfId="562" priority="153"/>
+    <cfRule type="duplicateValues" dxfId="508" priority="152"/>
+    <cfRule type="duplicateValues" dxfId="507" priority="153"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F140">
-    <cfRule type="duplicateValues" dxfId="561" priority="154"/>
-    <cfRule type="duplicateValues" dxfId="560" priority="155"/>
+    <cfRule type="duplicateValues" dxfId="506" priority="154"/>
+    <cfRule type="duplicateValues" dxfId="505" priority="155"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F140">
-    <cfRule type="duplicateValues" dxfId="559" priority="156"/>
+    <cfRule type="duplicateValues" dxfId="504" priority="156"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G140">
-    <cfRule type="duplicateValues" dxfId="558" priority="150"/>
+    <cfRule type="duplicateValues" dxfId="503" priority="150"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H140">
-    <cfRule type="cellIs" dxfId="557" priority="149" operator="equal">
+    <cfRule type="cellIs" dxfId="502" priority="149" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H142">
-    <cfRule type="cellIs" dxfId="556" priority="125" operator="equal">
+    <cfRule type="cellIs" dxfId="501" priority="125" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H141">
-    <cfRule type="cellIs" dxfId="555" priority="131" operator="equal">
+    <cfRule type="cellIs" dxfId="500" priority="131" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G141">
-    <cfRule type="duplicateValues" dxfId="554" priority="132"/>
-    <cfRule type="duplicateValues" dxfId="553" priority="133"/>
+    <cfRule type="duplicateValues" dxfId="499" priority="132"/>
+    <cfRule type="duplicateValues" dxfId="498" priority="133"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F141">
-    <cfRule type="duplicateValues" dxfId="552" priority="134"/>
-    <cfRule type="duplicateValues" dxfId="551" priority="135"/>
+    <cfRule type="duplicateValues" dxfId="497" priority="134"/>
+    <cfRule type="duplicateValues" dxfId="496" priority="135"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F141">
-    <cfRule type="duplicateValues" dxfId="550" priority="136"/>
+    <cfRule type="duplicateValues" dxfId="495" priority="136"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G142">
-    <cfRule type="duplicateValues" dxfId="549" priority="126"/>
-    <cfRule type="duplicateValues" dxfId="548" priority="127"/>
+    <cfRule type="duplicateValues" dxfId="494" priority="126"/>
+    <cfRule type="duplicateValues" dxfId="493" priority="127"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F142">
-    <cfRule type="duplicateValues" dxfId="547" priority="128"/>
-    <cfRule type="duplicateValues" dxfId="546" priority="129"/>
+    <cfRule type="duplicateValues" dxfId="492" priority="128"/>
+    <cfRule type="duplicateValues" dxfId="491" priority="129"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F142">
-    <cfRule type="duplicateValues" dxfId="545" priority="130"/>
+    <cfRule type="duplicateValues" dxfId="490" priority="130"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H143">
-    <cfRule type="cellIs" dxfId="544" priority="119" operator="equal">
+    <cfRule type="cellIs" dxfId="489" priority="119" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G143">
-    <cfRule type="duplicateValues" dxfId="543" priority="120"/>
-    <cfRule type="duplicateValues" dxfId="542" priority="121"/>
+    <cfRule type="duplicateValues" dxfId="488" priority="120"/>
+    <cfRule type="duplicateValues" dxfId="487" priority="121"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F143">
-    <cfRule type="duplicateValues" dxfId="541" priority="122"/>
-    <cfRule type="duplicateValues" dxfId="540" priority="123"/>
+    <cfRule type="duplicateValues" dxfId="486" priority="122"/>
+    <cfRule type="duplicateValues" dxfId="485" priority="123"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F143">
-    <cfRule type="duplicateValues" dxfId="539" priority="124"/>
+    <cfRule type="duplicateValues" dxfId="484" priority="124"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G144">
-    <cfRule type="duplicateValues" dxfId="538" priority="386"/>
-    <cfRule type="duplicateValues" dxfId="537" priority="387"/>
+    <cfRule type="duplicateValues" dxfId="483" priority="386"/>
+    <cfRule type="duplicateValues" dxfId="482" priority="387"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F144">
-    <cfRule type="duplicateValues" dxfId="536" priority="388"/>
-    <cfRule type="duplicateValues" dxfId="535" priority="389"/>
+    <cfRule type="duplicateValues" dxfId="481" priority="388"/>
+    <cfRule type="duplicateValues" dxfId="480" priority="389"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F144">
-    <cfRule type="duplicateValues" dxfId="534" priority="390"/>
+    <cfRule type="duplicateValues" dxfId="479" priority="390"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G137">
-    <cfRule type="duplicateValues" dxfId="533" priority="391"/>
-    <cfRule type="duplicateValues" dxfId="532" priority="392"/>
+    <cfRule type="duplicateValues" dxfId="478" priority="391"/>
+    <cfRule type="duplicateValues" dxfId="477" priority="392"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F137">
-    <cfRule type="duplicateValues" dxfId="531" priority="393"/>
-    <cfRule type="duplicateValues" dxfId="530" priority="394"/>
+    <cfRule type="duplicateValues" dxfId="476" priority="393"/>
+    <cfRule type="duplicateValues" dxfId="475" priority="394"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F137">
-    <cfRule type="duplicateValues" dxfId="529" priority="395"/>
+    <cfRule type="duplicateValues" dxfId="474" priority="395"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -75248,1187 +74643,1187 @@
   </sheetData>
   <autoFilter ref="A1:CG24"/>
   <conditionalFormatting sqref="F2">
-    <cfRule type="duplicateValues" dxfId="528" priority="757"/>
+    <cfRule type="duplicateValues" dxfId="473" priority="757"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2">
-    <cfRule type="duplicateValues" dxfId="527" priority="758"/>
-    <cfRule type="duplicateValues" dxfId="526" priority="759"/>
+    <cfRule type="duplicateValues" dxfId="472" priority="758"/>
+    <cfRule type="duplicateValues" dxfId="471" priority="759"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2">
-    <cfRule type="duplicateValues" dxfId="525" priority="760"/>
+    <cfRule type="duplicateValues" dxfId="470" priority="760"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3">
-    <cfRule type="duplicateValues" dxfId="524" priority="749"/>
+    <cfRule type="duplicateValues" dxfId="469" priority="749"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3">
-    <cfRule type="duplicateValues" dxfId="523" priority="750"/>
-    <cfRule type="duplicateValues" dxfId="522" priority="751"/>
+    <cfRule type="duplicateValues" dxfId="468" priority="750"/>
+    <cfRule type="duplicateValues" dxfId="467" priority="751"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3">
-    <cfRule type="duplicateValues" dxfId="521" priority="752"/>
+    <cfRule type="duplicateValues" dxfId="466" priority="752"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4:F6">
-    <cfRule type="duplicateValues" dxfId="520" priority="741"/>
+    <cfRule type="duplicateValues" dxfId="465" priority="741"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4:F6">
-    <cfRule type="duplicateValues" dxfId="519" priority="742"/>
-    <cfRule type="duplicateValues" dxfId="518" priority="743"/>
+    <cfRule type="duplicateValues" dxfId="464" priority="742"/>
+    <cfRule type="duplicateValues" dxfId="463" priority="743"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4:F6">
-    <cfRule type="duplicateValues" dxfId="517" priority="744"/>
+    <cfRule type="duplicateValues" dxfId="462" priority="744"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7">
-    <cfRule type="duplicateValues" dxfId="516" priority="733"/>
+    <cfRule type="duplicateValues" dxfId="461" priority="733"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7">
-    <cfRule type="duplicateValues" dxfId="515" priority="734"/>
-    <cfRule type="duplicateValues" dxfId="514" priority="735"/>
+    <cfRule type="duplicateValues" dxfId="460" priority="734"/>
+    <cfRule type="duplicateValues" dxfId="459" priority="735"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7">
-    <cfRule type="duplicateValues" dxfId="513" priority="736"/>
+    <cfRule type="duplicateValues" dxfId="458" priority="736"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8">
-    <cfRule type="duplicateValues" dxfId="512" priority="725"/>
+    <cfRule type="duplicateValues" dxfId="457" priority="725"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8">
-    <cfRule type="duplicateValues" dxfId="511" priority="726"/>
-    <cfRule type="duplicateValues" dxfId="510" priority="727"/>
+    <cfRule type="duplicateValues" dxfId="456" priority="726"/>
+    <cfRule type="duplicateValues" dxfId="455" priority="727"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8">
-    <cfRule type="duplicateValues" dxfId="509" priority="728"/>
+    <cfRule type="duplicateValues" dxfId="454" priority="728"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F9">
-    <cfRule type="duplicateValues" dxfId="508" priority="717"/>
+    <cfRule type="duplicateValues" dxfId="453" priority="717"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F9">
-    <cfRule type="duplicateValues" dxfId="507" priority="718"/>
-    <cfRule type="duplicateValues" dxfId="506" priority="719"/>
+    <cfRule type="duplicateValues" dxfId="452" priority="718"/>
+    <cfRule type="duplicateValues" dxfId="451" priority="719"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F9">
-    <cfRule type="duplicateValues" dxfId="505" priority="720"/>
+    <cfRule type="duplicateValues" dxfId="450" priority="720"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F10">
-    <cfRule type="duplicateValues" dxfId="504" priority="709"/>
+    <cfRule type="duplicateValues" dxfId="449" priority="709"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F10">
-    <cfRule type="duplicateValues" dxfId="503" priority="710"/>
-    <cfRule type="duplicateValues" dxfId="502" priority="711"/>
+    <cfRule type="duplicateValues" dxfId="448" priority="710"/>
+    <cfRule type="duplicateValues" dxfId="447" priority="711"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F10">
-    <cfRule type="duplicateValues" dxfId="501" priority="712"/>
+    <cfRule type="duplicateValues" dxfId="446" priority="712"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F11">
-    <cfRule type="duplicateValues" dxfId="500" priority="701"/>
+    <cfRule type="duplicateValues" dxfId="445" priority="701"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F11">
-    <cfRule type="duplicateValues" dxfId="499" priority="702"/>
-    <cfRule type="duplicateValues" dxfId="498" priority="703"/>
+    <cfRule type="duplicateValues" dxfId="444" priority="702"/>
+    <cfRule type="duplicateValues" dxfId="443" priority="703"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F11">
-    <cfRule type="duplicateValues" dxfId="497" priority="704"/>
+    <cfRule type="duplicateValues" dxfId="442" priority="704"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F12">
-    <cfRule type="duplicateValues" dxfId="496" priority="693"/>
+    <cfRule type="duplicateValues" dxfId="441" priority="693"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F12">
-    <cfRule type="duplicateValues" dxfId="495" priority="694"/>
-    <cfRule type="duplicateValues" dxfId="494" priority="695"/>
+    <cfRule type="duplicateValues" dxfId="440" priority="694"/>
+    <cfRule type="duplicateValues" dxfId="439" priority="695"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F12">
-    <cfRule type="duplicateValues" dxfId="493" priority="696"/>
+    <cfRule type="duplicateValues" dxfId="438" priority="696"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F13">
-    <cfRule type="duplicateValues" dxfId="492" priority="685"/>
+    <cfRule type="duplicateValues" dxfId="437" priority="685"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F13">
-    <cfRule type="duplicateValues" dxfId="491" priority="686"/>
-    <cfRule type="duplicateValues" dxfId="490" priority="687"/>
+    <cfRule type="duplicateValues" dxfId="436" priority="686"/>
+    <cfRule type="duplicateValues" dxfId="435" priority="687"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F13">
-    <cfRule type="duplicateValues" dxfId="489" priority="688"/>
+    <cfRule type="duplicateValues" dxfId="434" priority="688"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F14">
-    <cfRule type="duplicateValues" dxfId="488" priority="677"/>
+    <cfRule type="duplicateValues" dxfId="433" priority="677"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F14">
-    <cfRule type="duplicateValues" dxfId="487" priority="678"/>
-    <cfRule type="duplicateValues" dxfId="486" priority="679"/>
+    <cfRule type="duplicateValues" dxfId="432" priority="678"/>
+    <cfRule type="duplicateValues" dxfId="431" priority="679"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F14">
-    <cfRule type="duplicateValues" dxfId="485" priority="680"/>
+    <cfRule type="duplicateValues" dxfId="430" priority="680"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15">
-    <cfRule type="duplicateValues" dxfId="484" priority="669"/>
+    <cfRule type="duplicateValues" dxfId="429" priority="669"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15">
-    <cfRule type="duplicateValues" dxfId="483" priority="670"/>
-    <cfRule type="duplicateValues" dxfId="482" priority="671"/>
+    <cfRule type="duplicateValues" dxfId="428" priority="670"/>
+    <cfRule type="duplicateValues" dxfId="427" priority="671"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15">
-    <cfRule type="duplicateValues" dxfId="481" priority="672"/>
+    <cfRule type="duplicateValues" dxfId="426" priority="672"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16">
-    <cfRule type="duplicateValues" dxfId="480" priority="661"/>
+    <cfRule type="duplicateValues" dxfId="425" priority="661"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16">
-    <cfRule type="duplicateValues" dxfId="479" priority="662"/>
-    <cfRule type="duplicateValues" dxfId="478" priority="663"/>
+    <cfRule type="duplicateValues" dxfId="424" priority="662"/>
+    <cfRule type="duplicateValues" dxfId="423" priority="663"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16">
-    <cfRule type="duplicateValues" dxfId="477" priority="664"/>
+    <cfRule type="duplicateValues" dxfId="422" priority="664"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F17">
-    <cfRule type="duplicateValues" dxfId="476" priority="653"/>
+    <cfRule type="duplicateValues" dxfId="421" priority="653"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F17">
-    <cfRule type="duplicateValues" dxfId="475" priority="654"/>
-    <cfRule type="duplicateValues" dxfId="474" priority="655"/>
+    <cfRule type="duplicateValues" dxfId="420" priority="654"/>
+    <cfRule type="duplicateValues" dxfId="419" priority="655"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F17">
-    <cfRule type="duplicateValues" dxfId="473" priority="656"/>
+    <cfRule type="duplicateValues" dxfId="418" priority="656"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F18">
-    <cfRule type="duplicateValues" dxfId="472" priority="645"/>
+    <cfRule type="duplicateValues" dxfId="417" priority="645"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F18">
-    <cfRule type="duplicateValues" dxfId="471" priority="646"/>
-    <cfRule type="duplicateValues" dxfId="470" priority="647"/>
+    <cfRule type="duplicateValues" dxfId="416" priority="646"/>
+    <cfRule type="duplicateValues" dxfId="415" priority="647"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F18">
-    <cfRule type="duplicateValues" dxfId="469" priority="648"/>
+    <cfRule type="duplicateValues" dxfId="414" priority="648"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F19">
-    <cfRule type="duplicateValues" dxfId="468" priority="637"/>
+    <cfRule type="duplicateValues" dxfId="413" priority="637"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F19">
-    <cfRule type="duplicateValues" dxfId="467" priority="638"/>
-    <cfRule type="duplicateValues" dxfId="466" priority="639"/>
+    <cfRule type="duplicateValues" dxfId="412" priority="638"/>
+    <cfRule type="duplicateValues" dxfId="411" priority="639"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F19">
-    <cfRule type="duplicateValues" dxfId="465" priority="640"/>
+    <cfRule type="duplicateValues" dxfId="410" priority="640"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F20">
-    <cfRule type="duplicateValues" dxfId="464" priority="629"/>
+    <cfRule type="duplicateValues" dxfId="409" priority="629"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F20">
-    <cfRule type="duplicateValues" dxfId="463" priority="630"/>
-    <cfRule type="duplicateValues" dxfId="462" priority="631"/>
+    <cfRule type="duplicateValues" dxfId="408" priority="630"/>
+    <cfRule type="duplicateValues" dxfId="407" priority="631"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F20">
-    <cfRule type="duplicateValues" dxfId="461" priority="632"/>
+    <cfRule type="duplicateValues" dxfId="406" priority="632"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F21">
-    <cfRule type="duplicateValues" dxfId="460" priority="621"/>
+    <cfRule type="duplicateValues" dxfId="405" priority="621"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F21">
-    <cfRule type="duplicateValues" dxfId="459" priority="622"/>
-    <cfRule type="duplicateValues" dxfId="458" priority="623"/>
+    <cfRule type="duplicateValues" dxfId="404" priority="622"/>
+    <cfRule type="duplicateValues" dxfId="403" priority="623"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F21">
-    <cfRule type="duplicateValues" dxfId="457" priority="624"/>
+    <cfRule type="duplicateValues" dxfId="402" priority="624"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F22:F23">
-    <cfRule type="duplicateValues" dxfId="456" priority="613"/>
+    <cfRule type="duplicateValues" dxfId="401" priority="613"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F22:F23">
-    <cfRule type="duplicateValues" dxfId="455" priority="614"/>
-    <cfRule type="duplicateValues" dxfId="454" priority="615"/>
+    <cfRule type="duplicateValues" dxfId="400" priority="614"/>
+    <cfRule type="duplicateValues" dxfId="399" priority="615"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F22:F23">
-    <cfRule type="duplicateValues" dxfId="453" priority="616"/>
+    <cfRule type="duplicateValues" dxfId="398" priority="616"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F24">
-    <cfRule type="duplicateValues" dxfId="452" priority="605"/>
+    <cfRule type="duplicateValues" dxfId="397" priority="605"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F24">
-    <cfRule type="duplicateValues" dxfId="451" priority="606"/>
-    <cfRule type="duplicateValues" dxfId="450" priority="607"/>
+    <cfRule type="duplicateValues" dxfId="396" priority="606"/>
+    <cfRule type="duplicateValues" dxfId="395" priority="607"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F24">
-    <cfRule type="duplicateValues" dxfId="449" priority="608"/>
+    <cfRule type="duplicateValues" dxfId="394" priority="608"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F26">
-    <cfRule type="duplicateValues" dxfId="448" priority="597"/>
+    <cfRule type="duplicateValues" dxfId="393" priority="597"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F26">
-    <cfRule type="duplicateValues" dxfId="447" priority="598"/>
-    <cfRule type="duplicateValues" dxfId="446" priority="599"/>
+    <cfRule type="duplicateValues" dxfId="392" priority="598"/>
+    <cfRule type="duplicateValues" dxfId="391" priority="599"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F26">
-    <cfRule type="duplicateValues" dxfId="445" priority="600"/>
+    <cfRule type="duplicateValues" dxfId="390" priority="600"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F27">
-    <cfRule type="duplicateValues" dxfId="444" priority="592"/>
+    <cfRule type="duplicateValues" dxfId="389" priority="592"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F27">
-    <cfRule type="duplicateValues" dxfId="443" priority="593"/>
-    <cfRule type="duplicateValues" dxfId="442" priority="594"/>
+    <cfRule type="duplicateValues" dxfId="388" priority="593"/>
+    <cfRule type="duplicateValues" dxfId="387" priority="594"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F27">
-    <cfRule type="duplicateValues" dxfId="441" priority="595"/>
+    <cfRule type="duplicateValues" dxfId="386" priority="595"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F28">
-    <cfRule type="duplicateValues" dxfId="440" priority="586"/>
+    <cfRule type="duplicateValues" dxfId="385" priority="586"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F28">
-    <cfRule type="duplicateValues" dxfId="439" priority="587"/>
-    <cfRule type="duplicateValues" dxfId="438" priority="588"/>
+    <cfRule type="duplicateValues" dxfId="384" priority="587"/>
+    <cfRule type="duplicateValues" dxfId="383" priority="588"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F28">
-    <cfRule type="duplicateValues" dxfId="437" priority="589"/>
+    <cfRule type="duplicateValues" dxfId="382" priority="589"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F29:F30">
-    <cfRule type="duplicateValues" dxfId="436" priority="580"/>
+    <cfRule type="duplicateValues" dxfId="381" priority="580"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F29:F30">
-    <cfRule type="duplicateValues" dxfId="435" priority="581"/>
-    <cfRule type="duplicateValues" dxfId="434" priority="582"/>
+    <cfRule type="duplicateValues" dxfId="380" priority="581"/>
+    <cfRule type="duplicateValues" dxfId="379" priority="582"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F29:F30">
-    <cfRule type="duplicateValues" dxfId="433" priority="583"/>
+    <cfRule type="duplicateValues" dxfId="378" priority="583"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F31">
-    <cfRule type="duplicateValues" dxfId="432" priority="574"/>
+    <cfRule type="duplicateValues" dxfId="377" priority="574"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F31">
-    <cfRule type="duplicateValues" dxfId="431" priority="575"/>
-    <cfRule type="duplicateValues" dxfId="430" priority="576"/>
+    <cfRule type="duplicateValues" dxfId="376" priority="575"/>
+    <cfRule type="duplicateValues" dxfId="375" priority="576"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F31">
-    <cfRule type="duplicateValues" dxfId="429" priority="577"/>
+    <cfRule type="duplicateValues" dxfId="374" priority="577"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F32:F33">
-    <cfRule type="duplicateValues" dxfId="428" priority="568"/>
+    <cfRule type="duplicateValues" dxfId="373" priority="568"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F32:F33">
-    <cfRule type="duplicateValues" dxfId="427" priority="569"/>
-    <cfRule type="duplicateValues" dxfId="426" priority="570"/>
+    <cfRule type="duplicateValues" dxfId="372" priority="569"/>
+    <cfRule type="duplicateValues" dxfId="371" priority="570"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F32:F33">
-    <cfRule type="duplicateValues" dxfId="425" priority="571"/>
+    <cfRule type="duplicateValues" dxfId="370" priority="571"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F34">
-    <cfRule type="duplicateValues" dxfId="424" priority="562"/>
+    <cfRule type="duplicateValues" dxfId="369" priority="562"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F34">
-    <cfRule type="duplicateValues" dxfId="423" priority="563"/>
-    <cfRule type="duplicateValues" dxfId="422" priority="564"/>
+    <cfRule type="duplicateValues" dxfId="368" priority="563"/>
+    <cfRule type="duplicateValues" dxfId="367" priority="564"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F34">
-    <cfRule type="duplicateValues" dxfId="421" priority="565"/>
+    <cfRule type="duplicateValues" dxfId="366" priority="565"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F35">
-    <cfRule type="duplicateValues" dxfId="420" priority="556"/>
+    <cfRule type="duplicateValues" dxfId="365" priority="556"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F35">
-    <cfRule type="duplicateValues" dxfId="419" priority="557"/>
-    <cfRule type="duplicateValues" dxfId="418" priority="558"/>
+    <cfRule type="duplicateValues" dxfId="364" priority="557"/>
+    <cfRule type="duplicateValues" dxfId="363" priority="558"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F35">
-    <cfRule type="duplicateValues" dxfId="417" priority="559"/>
+    <cfRule type="duplicateValues" dxfId="362" priority="559"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F36">
-    <cfRule type="duplicateValues" dxfId="416" priority="550"/>
+    <cfRule type="duplicateValues" dxfId="361" priority="550"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F36">
-    <cfRule type="duplicateValues" dxfId="415" priority="551"/>
-    <cfRule type="duplicateValues" dxfId="414" priority="552"/>
+    <cfRule type="duplicateValues" dxfId="360" priority="551"/>
+    <cfRule type="duplicateValues" dxfId="359" priority="552"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F36">
-    <cfRule type="duplicateValues" dxfId="413" priority="553"/>
+    <cfRule type="duplicateValues" dxfId="358" priority="553"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F37">
-    <cfRule type="duplicateValues" dxfId="412" priority="543"/>
+    <cfRule type="duplicateValues" dxfId="357" priority="543"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F37">
-    <cfRule type="duplicateValues" dxfId="411" priority="544"/>
-    <cfRule type="duplicateValues" dxfId="410" priority="545"/>
+    <cfRule type="duplicateValues" dxfId="356" priority="544"/>
+    <cfRule type="duplicateValues" dxfId="355" priority="545"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F37">
-    <cfRule type="duplicateValues" dxfId="409" priority="546"/>
+    <cfRule type="duplicateValues" dxfId="354" priority="546"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F38">
-    <cfRule type="duplicateValues" dxfId="408" priority="537"/>
+    <cfRule type="duplicateValues" dxfId="353" priority="537"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F38">
-    <cfRule type="duplicateValues" dxfId="407" priority="538"/>
-    <cfRule type="duplicateValues" dxfId="406" priority="539"/>
+    <cfRule type="duplicateValues" dxfId="352" priority="538"/>
+    <cfRule type="duplicateValues" dxfId="351" priority="539"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F38">
-    <cfRule type="duplicateValues" dxfId="405" priority="540"/>
+    <cfRule type="duplicateValues" dxfId="350" priority="540"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F39">
-    <cfRule type="duplicateValues" dxfId="404" priority="531"/>
+    <cfRule type="duplicateValues" dxfId="349" priority="531"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F39">
-    <cfRule type="duplicateValues" dxfId="403" priority="532"/>
-    <cfRule type="duplicateValues" dxfId="402" priority="533"/>
+    <cfRule type="duplicateValues" dxfId="348" priority="532"/>
+    <cfRule type="duplicateValues" dxfId="347" priority="533"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F39">
-    <cfRule type="duplicateValues" dxfId="401" priority="534"/>
+    <cfRule type="duplicateValues" dxfId="346" priority="534"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F41">
-    <cfRule type="duplicateValues" dxfId="400" priority="525"/>
+    <cfRule type="duplicateValues" dxfId="345" priority="525"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F41">
-    <cfRule type="duplicateValues" dxfId="399" priority="526"/>
-    <cfRule type="duplicateValues" dxfId="398" priority="527"/>
+    <cfRule type="duplicateValues" dxfId="344" priority="526"/>
+    <cfRule type="duplicateValues" dxfId="343" priority="527"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F41">
-    <cfRule type="duplicateValues" dxfId="397" priority="528"/>
+    <cfRule type="duplicateValues" dxfId="342" priority="528"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F42">
-    <cfRule type="duplicateValues" dxfId="396" priority="519"/>
+    <cfRule type="duplicateValues" dxfId="341" priority="519"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F42">
-    <cfRule type="duplicateValues" dxfId="395" priority="520"/>
-    <cfRule type="duplicateValues" dxfId="394" priority="521"/>
+    <cfRule type="duplicateValues" dxfId="340" priority="520"/>
+    <cfRule type="duplicateValues" dxfId="339" priority="521"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F42">
-    <cfRule type="duplicateValues" dxfId="393" priority="522"/>
+    <cfRule type="duplicateValues" dxfId="338" priority="522"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F43">
-    <cfRule type="duplicateValues" dxfId="392" priority="513"/>
+    <cfRule type="duplicateValues" dxfId="337" priority="513"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F43">
-    <cfRule type="duplicateValues" dxfId="391" priority="514"/>
-    <cfRule type="duplicateValues" dxfId="390" priority="515"/>
+    <cfRule type="duplicateValues" dxfId="336" priority="514"/>
+    <cfRule type="duplicateValues" dxfId="335" priority="515"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F43">
-    <cfRule type="duplicateValues" dxfId="389" priority="516"/>
+    <cfRule type="duplicateValues" dxfId="334" priority="516"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F44">
-    <cfRule type="duplicateValues" dxfId="388" priority="507"/>
+    <cfRule type="duplicateValues" dxfId="333" priority="507"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F44">
-    <cfRule type="duplicateValues" dxfId="387" priority="508"/>
-    <cfRule type="duplicateValues" dxfId="386" priority="509"/>
+    <cfRule type="duplicateValues" dxfId="332" priority="508"/>
+    <cfRule type="duplicateValues" dxfId="331" priority="509"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F44">
-    <cfRule type="duplicateValues" dxfId="385" priority="510"/>
+    <cfRule type="duplicateValues" dxfId="330" priority="510"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F45">
-    <cfRule type="duplicateValues" dxfId="384" priority="499"/>
+    <cfRule type="duplicateValues" dxfId="329" priority="499"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F45">
-    <cfRule type="duplicateValues" dxfId="383" priority="500"/>
-    <cfRule type="duplicateValues" dxfId="382" priority="501"/>
+    <cfRule type="duplicateValues" dxfId="328" priority="500"/>
+    <cfRule type="duplicateValues" dxfId="327" priority="501"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F45">
-    <cfRule type="duplicateValues" dxfId="381" priority="502"/>
+    <cfRule type="duplicateValues" dxfId="326" priority="502"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F46">
-    <cfRule type="duplicateValues" dxfId="380" priority="493"/>
+    <cfRule type="duplicateValues" dxfId="325" priority="493"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F46">
-    <cfRule type="duplicateValues" dxfId="379" priority="494"/>
-    <cfRule type="duplicateValues" dxfId="378" priority="495"/>
+    <cfRule type="duplicateValues" dxfId="324" priority="494"/>
+    <cfRule type="duplicateValues" dxfId="323" priority="495"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F46">
-    <cfRule type="duplicateValues" dxfId="377" priority="496"/>
+    <cfRule type="duplicateValues" dxfId="322" priority="496"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F47">
-    <cfRule type="duplicateValues" dxfId="376" priority="487"/>
+    <cfRule type="duplicateValues" dxfId="321" priority="487"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F47">
-    <cfRule type="duplicateValues" dxfId="375" priority="488"/>
-    <cfRule type="duplicateValues" dxfId="374" priority="489"/>
+    <cfRule type="duplicateValues" dxfId="320" priority="488"/>
+    <cfRule type="duplicateValues" dxfId="319" priority="489"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F47">
-    <cfRule type="duplicateValues" dxfId="373" priority="490"/>
+    <cfRule type="duplicateValues" dxfId="318" priority="490"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F48">
-    <cfRule type="duplicateValues" dxfId="372" priority="481"/>
+    <cfRule type="duplicateValues" dxfId="317" priority="481"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F48">
-    <cfRule type="duplicateValues" dxfId="371" priority="482"/>
-    <cfRule type="duplicateValues" dxfId="370" priority="483"/>
+    <cfRule type="duplicateValues" dxfId="316" priority="482"/>
+    <cfRule type="duplicateValues" dxfId="315" priority="483"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F48">
-    <cfRule type="duplicateValues" dxfId="369" priority="484"/>
+    <cfRule type="duplicateValues" dxfId="314" priority="484"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F49">
-    <cfRule type="duplicateValues" dxfId="368" priority="475"/>
+    <cfRule type="duplicateValues" dxfId="313" priority="475"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F49">
-    <cfRule type="duplicateValues" dxfId="367" priority="476"/>
-    <cfRule type="duplicateValues" dxfId="366" priority="477"/>
+    <cfRule type="duplicateValues" dxfId="312" priority="476"/>
+    <cfRule type="duplicateValues" dxfId="311" priority="477"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F49">
-    <cfRule type="duplicateValues" dxfId="365" priority="478"/>
+    <cfRule type="duplicateValues" dxfId="310" priority="478"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F50">
-    <cfRule type="duplicateValues" dxfId="364" priority="469"/>
+    <cfRule type="duplicateValues" dxfId="309" priority="469"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F50">
-    <cfRule type="duplicateValues" dxfId="363" priority="470"/>
-    <cfRule type="duplicateValues" dxfId="362" priority="471"/>
+    <cfRule type="duplicateValues" dxfId="308" priority="470"/>
+    <cfRule type="duplicateValues" dxfId="307" priority="471"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F50">
-    <cfRule type="duplicateValues" dxfId="361" priority="472"/>
+    <cfRule type="duplicateValues" dxfId="306" priority="472"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F51">
-    <cfRule type="duplicateValues" dxfId="360" priority="461"/>
+    <cfRule type="duplicateValues" dxfId="305" priority="461"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F51">
-    <cfRule type="duplicateValues" dxfId="359" priority="462"/>
-    <cfRule type="duplicateValues" dxfId="358" priority="463"/>
+    <cfRule type="duplicateValues" dxfId="304" priority="462"/>
+    <cfRule type="duplicateValues" dxfId="303" priority="463"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F51">
-    <cfRule type="duplicateValues" dxfId="357" priority="464"/>
+    <cfRule type="duplicateValues" dxfId="302" priority="464"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F52">
-    <cfRule type="duplicateValues" dxfId="356" priority="455"/>
+    <cfRule type="duplicateValues" dxfId="301" priority="455"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F52">
-    <cfRule type="duplicateValues" dxfId="355" priority="456"/>
-    <cfRule type="duplicateValues" dxfId="354" priority="457"/>
+    <cfRule type="duplicateValues" dxfId="300" priority="456"/>
+    <cfRule type="duplicateValues" dxfId="299" priority="457"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F52">
-    <cfRule type="duplicateValues" dxfId="353" priority="458"/>
+    <cfRule type="duplicateValues" dxfId="298" priority="458"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F53">
-    <cfRule type="duplicateValues" dxfId="352" priority="449"/>
+    <cfRule type="duplicateValues" dxfId="297" priority="449"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F53">
-    <cfRule type="duplicateValues" dxfId="351" priority="450"/>
-    <cfRule type="duplicateValues" dxfId="350" priority="451"/>
+    <cfRule type="duplicateValues" dxfId="296" priority="450"/>
+    <cfRule type="duplicateValues" dxfId="295" priority="451"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F53">
-    <cfRule type="duplicateValues" dxfId="349" priority="452"/>
+    <cfRule type="duplicateValues" dxfId="294" priority="452"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F54">
-    <cfRule type="duplicateValues" dxfId="348" priority="443"/>
+    <cfRule type="duplicateValues" dxfId="293" priority="443"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F54">
-    <cfRule type="duplicateValues" dxfId="347" priority="444"/>
-    <cfRule type="duplicateValues" dxfId="346" priority="445"/>
+    <cfRule type="duplicateValues" dxfId="292" priority="444"/>
+    <cfRule type="duplicateValues" dxfId="291" priority="445"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F55">
-    <cfRule type="duplicateValues" dxfId="345" priority="438"/>
+    <cfRule type="duplicateValues" dxfId="290" priority="438"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F55">
-    <cfRule type="duplicateValues" dxfId="344" priority="439"/>
-    <cfRule type="duplicateValues" dxfId="343" priority="440"/>
+    <cfRule type="duplicateValues" dxfId="289" priority="439"/>
+    <cfRule type="duplicateValues" dxfId="288" priority="440"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F55">
-    <cfRule type="duplicateValues" dxfId="342" priority="441"/>
+    <cfRule type="duplicateValues" dxfId="287" priority="441"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F57">
-    <cfRule type="duplicateValues" dxfId="341" priority="432"/>
+    <cfRule type="duplicateValues" dxfId="286" priority="432"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F57">
-    <cfRule type="duplicateValues" dxfId="340" priority="433"/>
-    <cfRule type="duplicateValues" dxfId="339" priority="434"/>
+    <cfRule type="duplicateValues" dxfId="285" priority="433"/>
+    <cfRule type="duplicateValues" dxfId="284" priority="434"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F57">
-    <cfRule type="duplicateValues" dxfId="338" priority="435"/>
+    <cfRule type="duplicateValues" dxfId="283" priority="435"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F58">
-    <cfRule type="duplicateValues" dxfId="337" priority="426"/>
+    <cfRule type="duplicateValues" dxfId="282" priority="426"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F58">
-    <cfRule type="duplicateValues" dxfId="336" priority="427"/>
-    <cfRule type="duplicateValues" dxfId="335" priority="428"/>
+    <cfRule type="duplicateValues" dxfId="281" priority="427"/>
+    <cfRule type="duplicateValues" dxfId="280" priority="428"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F58">
-    <cfRule type="duplicateValues" dxfId="334" priority="429"/>
+    <cfRule type="duplicateValues" dxfId="279" priority="429"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F59:F61">
-    <cfRule type="duplicateValues" dxfId="333" priority="419"/>
+    <cfRule type="duplicateValues" dxfId="278" priority="419"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F59:F61">
-    <cfRule type="duplicateValues" dxfId="332" priority="420"/>
-    <cfRule type="duplicateValues" dxfId="331" priority="421"/>
+    <cfRule type="duplicateValues" dxfId="277" priority="420"/>
+    <cfRule type="duplicateValues" dxfId="276" priority="421"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F59:F61">
-    <cfRule type="duplicateValues" dxfId="330" priority="422"/>
+    <cfRule type="duplicateValues" dxfId="275" priority="422"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F62">
-    <cfRule type="duplicateValues" dxfId="329" priority="412"/>
+    <cfRule type="duplicateValues" dxfId="274" priority="412"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F62">
-    <cfRule type="duplicateValues" dxfId="328" priority="413"/>
-    <cfRule type="duplicateValues" dxfId="327" priority="414"/>
+    <cfRule type="duplicateValues" dxfId="273" priority="413"/>
+    <cfRule type="duplicateValues" dxfId="272" priority="414"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F62">
-    <cfRule type="duplicateValues" dxfId="326" priority="415"/>
+    <cfRule type="duplicateValues" dxfId="271" priority="415"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F63">
-    <cfRule type="duplicateValues" dxfId="325" priority="405"/>
+    <cfRule type="duplicateValues" dxfId="270" priority="405"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F63">
-    <cfRule type="duplicateValues" dxfId="324" priority="406"/>
-    <cfRule type="duplicateValues" dxfId="323" priority="407"/>
+    <cfRule type="duplicateValues" dxfId="269" priority="406"/>
+    <cfRule type="duplicateValues" dxfId="268" priority="407"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F63">
-    <cfRule type="duplicateValues" dxfId="322" priority="408"/>
+    <cfRule type="duplicateValues" dxfId="267" priority="408"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F64">
-    <cfRule type="duplicateValues" dxfId="321" priority="398"/>
+    <cfRule type="duplicateValues" dxfId="266" priority="398"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F64">
-    <cfRule type="duplicateValues" dxfId="320" priority="399"/>
-    <cfRule type="duplicateValues" dxfId="319" priority="400"/>
+    <cfRule type="duplicateValues" dxfId="265" priority="399"/>
+    <cfRule type="duplicateValues" dxfId="264" priority="400"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F64">
-    <cfRule type="duplicateValues" dxfId="318" priority="401"/>
+    <cfRule type="duplicateValues" dxfId="263" priority="401"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F65">
-    <cfRule type="duplicateValues" dxfId="317" priority="391"/>
+    <cfRule type="duplicateValues" dxfId="262" priority="391"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F65">
-    <cfRule type="duplicateValues" dxfId="316" priority="392"/>
-    <cfRule type="duplicateValues" dxfId="315" priority="393"/>
+    <cfRule type="duplicateValues" dxfId="261" priority="392"/>
+    <cfRule type="duplicateValues" dxfId="260" priority="393"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F65">
-    <cfRule type="duplicateValues" dxfId="314" priority="394"/>
+    <cfRule type="duplicateValues" dxfId="259" priority="394"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F66">
-    <cfRule type="duplicateValues" dxfId="313" priority="384"/>
+    <cfRule type="duplicateValues" dxfId="258" priority="384"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F66">
-    <cfRule type="duplicateValues" dxfId="312" priority="385"/>
-    <cfRule type="duplicateValues" dxfId="311" priority="386"/>
+    <cfRule type="duplicateValues" dxfId="257" priority="385"/>
+    <cfRule type="duplicateValues" dxfId="256" priority="386"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F66">
-    <cfRule type="duplicateValues" dxfId="310" priority="387"/>
+    <cfRule type="duplicateValues" dxfId="255" priority="387"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F67">
-    <cfRule type="duplicateValues" dxfId="309" priority="377"/>
+    <cfRule type="duplicateValues" dxfId="254" priority="377"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F67">
-    <cfRule type="duplicateValues" dxfId="308" priority="378"/>
-    <cfRule type="duplicateValues" dxfId="307" priority="379"/>
+    <cfRule type="duplicateValues" dxfId="253" priority="378"/>
+    <cfRule type="duplicateValues" dxfId="252" priority="379"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F67">
-    <cfRule type="duplicateValues" dxfId="306" priority="380"/>
+    <cfRule type="duplicateValues" dxfId="251" priority="380"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F68">
-    <cfRule type="duplicateValues" dxfId="305" priority="370"/>
+    <cfRule type="duplicateValues" dxfId="250" priority="370"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F68">
-    <cfRule type="duplicateValues" dxfId="304" priority="371"/>
-    <cfRule type="duplicateValues" dxfId="303" priority="372"/>
+    <cfRule type="duplicateValues" dxfId="249" priority="371"/>
+    <cfRule type="duplicateValues" dxfId="248" priority="372"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F68">
-    <cfRule type="duplicateValues" dxfId="302" priority="373"/>
+    <cfRule type="duplicateValues" dxfId="247" priority="373"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F69">
-    <cfRule type="duplicateValues" dxfId="301" priority="363"/>
+    <cfRule type="duplicateValues" dxfId="246" priority="363"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F69">
-    <cfRule type="duplicateValues" dxfId="300" priority="364"/>
-    <cfRule type="duplicateValues" dxfId="299" priority="365"/>
+    <cfRule type="duplicateValues" dxfId="245" priority="364"/>
+    <cfRule type="duplicateValues" dxfId="244" priority="365"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F69">
-    <cfRule type="duplicateValues" dxfId="298" priority="366"/>
+    <cfRule type="duplicateValues" dxfId="243" priority="366"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F70">
-    <cfRule type="duplicateValues" dxfId="297" priority="356"/>
+    <cfRule type="duplicateValues" dxfId="242" priority="356"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F70">
-    <cfRule type="duplicateValues" dxfId="296" priority="357"/>
-    <cfRule type="duplicateValues" dxfId="295" priority="358"/>
+    <cfRule type="duplicateValues" dxfId="241" priority="357"/>
+    <cfRule type="duplicateValues" dxfId="240" priority="358"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F70">
-    <cfRule type="duplicateValues" dxfId="294" priority="359"/>
+    <cfRule type="duplicateValues" dxfId="239" priority="359"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F71">
-    <cfRule type="duplicateValues" dxfId="293" priority="349"/>
+    <cfRule type="duplicateValues" dxfId="238" priority="349"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F71">
-    <cfRule type="duplicateValues" dxfId="292" priority="350"/>
-    <cfRule type="duplicateValues" dxfId="291" priority="351"/>
+    <cfRule type="duplicateValues" dxfId="237" priority="350"/>
+    <cfRule type="duplicateValues" dxfId="236" priority="351"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F71">
-    <cfRule type="duplicateValues" dxfId="290" priority="352"/>
+    <cfRule type="duplicateValues" dxfId="235" priority="352"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F72">
-    <cfRule type="duplicateValues" dxfId="289" priority="337"/>
+    <cfRule type="duplicateValues" dxfId="234" priority="337"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F72">
-    <cfRule type="duplicateValues" dxfId="288" priority="338"/>
-    <cfRule type="duplicateValues" dxfId="287" priority="339"/>
+    <cfRule type="duplicateValues" dxfId="233" priority="338"/>
+    <cfRule type="duplicateValues" dxfId="232" priority="339"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F72">
-    <cfRule type="duplicateValues" dxfId="286" priority="340"/>
+    <cfRule type="duplicateValues" dxfId="231" priority="340"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F73">
-    <cfRule type="duplicateValues" dxfId="285" priority="330"/>
+    <cfRule type="duplicateValues" dxfId="230" priority="330"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F73">
-    <cfRule type="duplicateValues" dxfId="284" priority="331"/>
-    <cfRule type="duplicateValues" dxfId="283" priority="332"/>
+    <cfRule type="duplicateValues" dxfId="229" priority="331"/>
+    <cfRule type="duplicateValues" dxfId="228" priority="332"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F73">
-    <cfRule type="duplicateValues" dxfId="282" priority="333"/>
+    <cfRule type="duplicateValues" dxfId="227" priority="333"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F74">
-    <cfRule type="duplicateValues" dxfId="281" priority="323"/>
+    <cfRule type="duplicateValues" dxfId="226" priority="323"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F74">
-    <cfRule type="duplicateValues" dxfId="280" priority="324"/>
-    <cfRule type="duplicateValues" dxfId="279" priority="325"/>
+    <cfRule type="duplicateValues" dxfId="225" priority="324"/>
+    <cfRule type="duplicateValues" dxfId="224" priority="325"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F74">
-    <cfRule type="duplicateValues" dxfId="278" priority="326"/>
+    <cfRule type="duplicateValues" dxfId="223" priority="326"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F75">
-    <cfRule type="duplicateValues" dxfId="277" priority="316"/>
+    <cfRule type="duplicateValues" dxfId="222" priority="316"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F75">
-    <cfRule type="duplicateValues" dxfId="276" priority="317"/>
-    <cfRule type="duplicateValues" dxfId="275" priority="318"/>
+    <cfRule type="duplicateValues" dxfId="221" priority="317"/>
+    <cfRule type="duplicateValues" dxfId="220" priority="318"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F75">
-    <cfRule type="duplicateValues" dxfId="274" priority="319"/>
+    <cfRule type="duplicateValues" dxfId="219" priority="319"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F76">
-    <cfRule type="duplicateValues" dxfId="273" priority="309"/>
+    <cfRule type="duplicateValues" dxfId="218" priority="309"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F76">
-    <cfRule type="duplicateValues" dxfId="272" priority="310"/>
-    <cfRule type="duplicateValues" dxfId="271" priority="311"/>
+    <cfRule type="duplicateValues" dxfId="217" priority="310"/>
+    <cfRule type="duplicateValues" dxfId="216" priority="311"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F76">
-    <cfRule type="duplicateValues" dxfId="270" priority="312"/>
+    <cfRule type="duplicateValues" dxfId="215" priority="312"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F77">
-    <cfRule type="duplicateValues" dxfId="269" priority="302"/>
+    <cfRule type="duplicateValues" dxfId="214" priority="302"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F77">
-    <cfRule type="duplicateValues" dxfId="268" priority="303"/>
-    <cfRule type="duplicateValues" dxfId="267" priority="304"/>
+    <cfRule type="duplicateValues" dxfId="213" priority="303"/>
+    <cfRule type="duplicateValues" dxfId="212" priority="304"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F77">
-    <cfRule type="duplicateValues" dxfId="266" priority="305"/>
+    <cfRule type="duplicateValues" dxfId="211" priority="305"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F78">
-    <cfRule type="duplicateValues" dxfId="265" priority="295"/>
+    <cfRule type="duplicateValues" dxfId="210" priority="295"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F78">
-    <cfRule type="duplicateValues" dxfId="264" priority="296"/>
-    <cfRule type="duplicateValues" dxfId="263" priority="297"/>
+    <cfRule type="duplicateValues" dxfId="209" priority="296"/>
+    <cfRule type="duplicateValues" dxfId="208" priority="297"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F78">
-    <cfRule type="duplicateValues" dxfId="262" priority="298"/>
+    <cfRule type="duplicateValues" dxfId="207" priority="298"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F79">
-    <cfRule type="duplicateValues" dxfId="261" priority="288"/>
+    <cfRule type="duplicateValues" dxfId="206" priority="288"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F79">
-    <cfRule type="duplicateValues" dxfId="260" priority="289"/>
-    <cfRule type="duplicateValues" dxfId="259" priority="290"/>
+    <cfRule type="duplicateValues" dxfId="205" priority="289"/>
+    <cfRule type="duplicateValues" dxfId="204" priority="290"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F79">
-    <cfRule type="duplicateValues" dxfId="258" priority="291"/>
+    <cfRule type="duplicateValues" dxfId="203" priority="291"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F80">
-    <cfRule type="duplicateValues" dxfId="257" priority="281"/>
+    <cfRule type="duplicateValues" dxfId="202" priority="281"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F80">
-    <cfRule type="duplicateValues" dxfId="256" priority="282"/>
-    <cfRule type="duplicateValues" dxfId="255" priority="283"/>
+    <cfRule type="duplicateValues" dxfId="201" priority="282"/>
+    <cfRule type="duplicateValues" dxfId="200" priority="283"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F80">
-    <cfRule type="duplicateValues" dxfId="254" priority="284"/>
+    <cfRule type="duplicateValues" dxfId="199" priority="284"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F81">
-    <cfRule type="duplicateValues" dxfId="253" priority="267"/>
+    <cfRule type="duplicateValues" dxfId="198" priority="267"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F81">
-    <cfRule type="duplicateValues" dxfId="252" priority="268"/>
-    <cfRule type="duplicateValues" dxfId="251" priority="269"/>
+    <cfRule type="duplicateValues" dxfId="197" priority="268"/>
+    <cfRule type="duplicateValues" dxfId="196" priority="269"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F81">
-    <cfRule type="duplicateValues" dxfId="250" priority="270"/>
+    <cfRule type="duplicateValues" dxfId="195" priority="270"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F82">
-    <cfRule type="duplicateValues" dxfId="249" priority="260"/>
+    <cfRule type="duplicateValues" dxfId="194" priority="260"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F82">
-    <cfRule type="duplicateValues" dxfId="248" priority="261"/>
-    <cfRule type="duplicateValues" dxfId="247" priority="262"/>
+    <cfRule type="duplicateValues" dxfId="193" priority="261"/>
+    <cfRule type="duplicateValues" dxfId="192" priority="262"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F82">
-    <cfRule type="duplicateValues" dxfId="246" priority="263"/>
+    <cfRule type="duplicateValues" dxfId="191" priority="263"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F83">
-    <cfRule type="duplicateValues" dxfId="245" priority="253"/>
+    <cfRule type="duplicateValues" dxfId="190" priority="253"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F83">
-    <cfRule type="duplicateValues" dxfId="244" priority="254"/>
-    <cfRule type="duplicateValues" dxfId="243" priority="255"/>
+    <cfRule type="duplicateValues" dxfId="189" priority="254"/>
+    <cfRule type="duplicateValues" dxfId="188" priority="255"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F83">
-    <cfRule type="duplicateValues" dxfId="242" priority="256"/>
+    <cfRule type="duplicateValues" dxfId="187" priority="256"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F84">
-    <cfRule type="duplicateValues" dxfId="241" priority="246"/>
+    <cfRule type="duplicateValues" dxfId="186" priority="246"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F84">
-    <cfRule type="duplicateValues" dxfId="240" priority="247"/>
-    <cfRule type="duplicateValues" dxfId="239" priority="248"/>
+    <cfRule type="duplicateValues" dxfId="185" priority="247"/>
+    <cfRule type="duplicateValues" dxfId="184" priority="248"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F84">
-    <cfRule type="duplicateValues" dxfId="238" priority="249"/>
+    <cfRule type="duplicateValues" dxfId="183" priority="249"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F86">
-    <cfRule type="duplicateValues" dxfId="237" priority="236"/>
+    <cfRule type="duplicateValues" dxfId="182" priority="236"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F86">
-    <cfRule type="duplicateValues" dxfId="236" priority="237"/>
-    <cfRule type="duplicateValues" dxfId="235" priority="238"/>
+    <cfRule type="duplicateValues" dxfId="181" priority="237"/>
+    <cfRule type="duplicateValues" dxfId="180" priority="238"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F86">
-    <cfRule type="duplicateValues" dxfId="234" priority="239"/>
+    <cfRule type="duplicateValues" dxfId="179" priority="239"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F87">
-    <cfRule type="duplicateValues" dxfId="233" priority="229"/>
+    <cfRule type="duplicateValues" dxfId="178" priority="229"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F87">
-    <cfRule type="duplicateValues" dxfId="232" priority="230"/>
-    <cfRule type="duplicateValues" dxfId="231" priority="231"/>
+    <cfRule type="duplicateValues" dxfId="177" priority="230"/>
+    <cfRule type="duplicateValues" dxfId="176" priority="231"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F87">
-    <cfRule type="duplicateValues" dxfId="230" priority="232"/>
+    <cfRule type="duplicateValues" dxfId="175" priority="232"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F88">
-    <cfRule type="duplicateValues" dxfId="229" priority="222"/>
+    <cfRule type="duplicateValues" dxfId="174" priority="222"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F88">
-    <cfRule type="duplicateValues" dxfId="228" priority="223"/>
-    <cfRule type="duplicateValues" dxfId="227" priority="224"/>
+    <cfRule type="duplicateValues" dxfId="173" priority="223"/>
+    <cfRule type="duplicateValues" dxfId="172" priority="224"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F88">
-    <cfRule type="duplicateValues" dxfId="226" priority="225"/>
+    <cfRule type="duplicateValues" dxfId="171" priority="225"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F89">
-    <cfRule type="duplicateValues" dxfId="225" priority="215"/>
+    <cfRule type="duplicateValues" dxfId="170" priority="215"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F89">
-    <cfRule type="duplicateValues" dxfId="224" priority="216"/>
-    <cfRule type="duplicateValues" dxfId="223" priority="217"/>
+    <cfRule type="duplicateValues" dxfId="169" priority="216"/>
+    <cfRule type="duplicateValues" dxfId="168" priority="217"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F89">
-    <cfRule type="duplicateValues" dxfId="222" priority="218"/>
+    <cfRule type="duplicateValues" dxfId="167" priority="218"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F90">
-    <cfRule type="duplicateValues" dxfId="221" priority="208"/>
+    <cfRule type="duplicateValues" dxfId="166" priority="208"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F90">
-    <cfRule type="duplicateValues" dxfId="220" priority="209"/>
-    <cfRule type="duplicateValues" dxfId="219" priority="210"/>
+    <cfRule type="duplicateValues" dxfId="165" priority="209"/>
+    <cfRule type="duplicateValues" dxfId="164" priority="210"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F90">
-    <cfRule type="duplicateValues" dxfId="218" priority="211"/>
+    <cfRule type="duplicateValues" dxfId="163" priority="211"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F91">
-    <cfRule type="duplicateValues" dxfId="217" priority="201"/>
+    <cfRule type="duplicateValues" dxfId="162" priority="201"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F91">
-    <cfRule type="duplicateValues" dxfId="216" priority="202"/>
-    <cfRule type="duplicateValues" dxfId="215" priority="203"/>
+    <cfRule type="duplicateValues" dxfId="161" priority="202"/>
+    <cfRule type="duplicateValues" dxfId="160" priority="203"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F91">
-    <cfRule type="duplicateValues" dxfId="214" priority="204"/>
+    <cfRule type="duplicateValues" dxfId="159" priority="204"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F92">
-    <cfRule type="duplicateValues" dxfId="213" priority="194"/>
+    <cfRule type="duplicateValues" dxfId="158" priority="194"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F92">
-    <cfRule type="duplicateValues" dxfId="212" priority="195"/>
-    <cfRule type="duplicateValues" dxfId="211" priority="196"/>
+    <cfRule type="duplicateValues" dxfId="157" priority="195"/>
+    <cfRule type="duplicateValues" dxfId="156" priority="196"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F92">
-    <cfRule type="duplicateValues" dxfId="210" priority="197"/>
+    <cfRule type="duplicateValues" dxfId="155" priority="197"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F93">
-    <cfRule type="duplicateValues" dxfId="209" priority="187"/>
+    <cfRule type="duplicateValues" dxfId="154" priority="187"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F93">
-    <cfRule type="duplicateValues" dxfId="208" priority="188"/>
-    <cfRule type="duplicateValues" dxfId="207" priority="189"/>
+    <cfRule type="duplicateValues" dxfId="153" priority="188"/>
+    <cfRule type="duplicateValues" dxfId="152" priority="189"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F93">
-    <cfRule type="duplicateValues" dxfId="206" priority="190"/>
+    <cfRule type="duplicateValues" dxfId="151" priority="190"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F94">
-    <cfRule type="duplicateValues" dxfId="205" priority="180"/>
+    <cfRule type="duplicateValues" dxfId="150" priority="180"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F94">
-    <cfRule type="duplicateValues" dxfId="204" priority="181"/>
-    <cfRule type="duplicateValues" dxfId="203" priority="182"/>
+    <cfRule type="duplicateValues" dxfId="149" priority="181"/>
+    <cfRule type="duplicateValues" dxfId="148" priority="182"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F94">
-    <cfRule type="duplicateValues" dxfId="202" priority="183"/>
+    <cfRule type="duplicateValues" dxfId="147" priority="183"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F95">
-    <cfRule type="duplicateValues" dxfId="201" priority="173"/>
+    <cfRule type="duplicateValues" dxfId="146" priority="173"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F95">
-    <cfRule type="duplicateValues" dxfId="200" priority="174"/>
-    <cfRule type="duplicateValues" dxfId="199" priority="175"/>
+    <cfRule type="duplicateValues" dxfId="145" priority="174"/>
+    <cfRule type="duplicateValues" dxfId="144" priority="175"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F95">
-    <cfRule type="duplicateValues" dxfId="198" priority="176"/>
+    <cfRule type="duplicateValues" dxfId="143" priority="176"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F96">
-    <cfRule type="duplicateValues" dxfId="197" priority="166"/>
-    <cfRule type="duplicateValues" dxfId="196" priority="167"/>
+    <cfRule type="duplicateValues" dxfId="142" priority="166"/>
+    <cfRule type="duplicateValues" dxfId="141" priority="167"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F96">
-    <cfRule type="duplicateValues" dxfId="195" priority="168"/>
+    <cfRule type="duplicateValues" dxfId="140" priority="168"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F96">
-    <cfRule type="duplicateValues" dxfId="194" priority="169"/>
+    <cfRule type="duplicateValues" dxfId="139" priority="169"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F97">
-    <cfRule type="duplicateValues" dxfId="193" priority="161"/>
-    <cfRule type="duplicateValues" dxfId="192" priority="162"/>
+    <cfRule type="duplicateValues" dxfId="138" priority="161"/>
+    <cfRule type="duplicateValues" dxfId="137" priority="162"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F97">
-    <cfRule type="duplicateValues" dxfId="191" priority="163"/>
+    <cfRule type="duplicateValues" dxfId="136" priority="163"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F97">
-    <cfRule type="duplicateValues" dxfId="190" priority="164"/>
+    <cfRule type="duplicateValues" dxfId="135" priority="164"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F98">
-    <cfRule type="duplicateValues" dxfId="189" priority="156"/>
-    <cfRule type="duplicateValues" dxfId="188" priority="157"/>
+    <cfRule type="duplicateValues" dxfId="134" priority="156"/>
+    <cfRule type="duplicateValues" dxfId="133" priority="157"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F98">
-    <cfRule type="duplicateValues" dxfId="187" priority="158"/>
+    <cfRule type="duplicateValues" dxfId="132" priority="158"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F98">
-    <cfRule type="duplicateValues" dxfId="186" priority="159"/>
+    <cfRule type="duplicateValues" dxfId="131" priority="159"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F99">
-    <cfRule type="duplicateValues" dxfId="185" priority="151"/>
-    <cfRule type="duplicateValues" dxfId="184" priority="152"/>
+    <cfRule type="duplicateValues" dxfId="130" priority="151"/>
+    <cfRule type="duplicateValues" dxfId="129" priority="152"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F99">
-    <cfRule type="duplicateValues" dxfId="183" priority="153"/>
+    <cfRule type="duplicateValues" dxfId="128" priority="153"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F99">
-    <cfRule type="duplicateValues" dxfId="182" priority="154"/>
+    <cfRule type="duplicateValues" dxfId="127" priority="154"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F100">
-    <cfRule type="duplicateValues" dxfId="181" priority="146"/>
-    <cfRule type="duplicateValues" dxfId="180" priority="147"/>
+    <cfRule type="duplicateValues" dxfId="126" priority="146"/>
+    <cfRule type="duplicateValues" dxfId="125" priority="147"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F100">
-    <cfRule type="duplicateValues" dxfId="179" priority="148"/>
+    <cfRule type="duplicateValues" dxfId="124" priority="148"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F100">
-    <cfRule type="duplicateValues" dxfId="178" priority="149"/>
+    <cfRule type="duplicateValues" dxfId="123" priority="149"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F101">
-    <cfRule type="duplicateValues" dxfId="177" priority="141"/>
-    <cfRule type="duplicateValues" dxfId="176" priority="142"/>
+    <cfRule type="duplicateValues" dxfId="122" priority="141"/>
+    <cfRule type="duplicateValues" dxfId="121" priority="142"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F101">
-    <cfRule type="duplicateValues" dxfId="175" priority="143"/>
+    <cfRule type="duplicateValues" dxfId="120" priority="143"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F101">
-    <cfRule type="duplicateValues" dxfId="174" priority="144"/>
+    <cfRule type="duplicateValues" dxfId="119" priority="144"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F102">
-    <cfRule type="duplicateValues" dxfId="173" priority="136"/>
-    <cfRule type="duplicateValues" dxfId="172" priority="137"/>
+    <cfRule type="duplicateValues" dxfId="118" priority="136"/>
+    <cfRule type="duplicateValues" dxfId="117" priority="137"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F102">
-    <cfRule type="duplicateValues" dxfId="171" priority="138"/>
+    <cfRule type="duplicateValues" dxfId="116" priority="138"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F102">
-    <cfRule type="duplicateValues" dxfId="170" priority="139"/>
+    <cfRule type="duplicateValues" dxfId="115" priority="139"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F103">
-    <cfRule type="duplicateValues" dxfId="169" priority="130"/>
-    <cfRule type="duplicateValues" dxfId="168" priority="131"/>
+    <cfRule type="duplicateValues" dxfId="114" priority="130"/>
+    <cfRule type="duplicateValues" dxfId="113" priority="131"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F103">
-    <cfRule type="duplicateValues" dxfId="167" priority="132"/>
+    <cfRule type="duplicateValues" dxfId="112" priority="132"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F103">
-    <cfRule type="duplicateValues" dxfId="166" priority="133"/>
+    <cfRule type="duplicateValues" dxfId="111" priority="133"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F104 F106">
-    <cfRule type="duplicateValues" dxfId="165" priority="124"/>
-    <cfRule type="duplicateValues" dxfId="164" priority="125"/>
+    <cfRule type="duplicateValues" dxfId="110" priority="124"/>
+    <cfRule type="duplicateValues" dxfId="109" priority="125"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F104 F106">
-    <cfRule type="duplicateValues" dxfId="163" priority="126"/>
+    <cfRule type="duplicateValues" dxfId="108" priority="126"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F107:F108">
-    <cfRule type="duplicateValues" dxfId="162" priority="118"/>
-    <cfRule type="duplicateValues" dxfId="161" priority="119"/>
+    <cfRule type="duplicateValues" dxfId="107" priority="118"/>
+    <cfRule type="duplicateValues" dxfId="106" priority="119"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F107:F108">
-    <cfRule type="duplicateValues" dxfId="160" priority="120"/>
+    <cfRule type="duplicateValues" dxfId="105" priority="120"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F107:F108">
-    <cfRule type="duplicateValues" dxfId="159" priority="121"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="121"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F109">
-    <cfRule type="duplicateValues" dxfId="158" priority="112"/>
-    <cfRule type="duplicateValues" dxfId="157" priority="113"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="112"/>
+    <cfRule type="duplicateValues" dxfId="102" priority="113"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F109">
-    <cfRule type="duplicateValues" dxfId="156" priority="114"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="114"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F109">
-    <cfRule type="duplicateValues" dxfId="155" priority="115"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="115"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F110">
-    <cfRule type="duplicateValues" dxfId="154" priority="106"/>
-    <cfRule type="duplicateValues" dxfId="153" priority="107"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="106"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="107"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F110">
-    <cfRule type="duplicateValues" dxfId="152" priority="108"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="108"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F110">
-    <cfRule type="duplicateValues" dxfId="151" priority="109"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="109"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F111">
-    <cfRule type="duplicateValues" dxfId="150" priority="100"/>
-    <cfRule type="duplicateValues" dxfId="149" priority="101"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="100"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="101"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F111">
-    <cfRule type="duplicateValues" dxfId="148" priority="102"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="102"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F111">
-    <cfRule type="duplicateValues" dxfId="147" priority="103"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="103"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F112">
-    <cfRule type="duplicateValues" dxfId="146" priority="96"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="96"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F112">
-    <cfRule type="duplicateValues" dxfId="145" priority="93"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="93"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F112">
-    <cfRule type="duplicateValues" dxfId="144" priority="94"/>
-    <cfRule type="duplicateValues" dxfId="143" priority="95"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="94"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="95"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F113">
-    <cfRule type="duplicateValues" dxfId="142" priority="91"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="91"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F113">
-    <cfRule type="duplicateValues" dxfId="141" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="88"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F113">
-    <cfRule type="duplicateValues" dxfId="140" priority="89"/>
-    <cfRule type="duplicateValues" dxfId="139" priority="90"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="90"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F114">
-    <cfRule type="duplicateValues" dxfId="138" priority="84"/>
-    <cfRule type="duplicateValues" dxfId="137" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="85"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F114">
-    <cfRule type="duplicateValues" dxfId="136" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="86"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F114">
-    <cfRule type="duplicateValues" dxfId="135" priority="87"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="87"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F115">
-    <cfRule type="duplicateValues" dxfId="134" priority="80"/>
-    <cfRule type="duplicateValues" dxfId="133" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="81"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F115">
-    <cfRule type="duplicateValues" dxfId="132" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="82"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F115">
-    <cfRule type="duplicateValues" dxfId="131" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="83"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F116">
-    <cfRule type="duplicateValues" dxfId="130" priority="76"/>
-    <cfRule type="duplicateValues" dxfId="129" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="77"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F116">
-    <cfRule type="duplicateValues" dxfId="128" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="78"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F116">
-    <cfRule type="duplicateValues" dxfId="127" priority="79"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="79"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F117">
-    <cfRule type="duplicateValues" dxfId="126" priority="72"/>
-    <cfRule type="duplicateValues" dxfId="125" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="73"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F117">
-    <cfRule type="duplicateValues" dxfId="124" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="74"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F117">
-    <cfRule type="duplicateValues" dxfId="123" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="75"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F118">
-    <cfRule type="duplicateValues" dxfId="122" priority="68"/>
-    <cfRule type="duplicateValues" dxfId="121" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="69"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F118">
-    <cfRule type="duplicateValues" dxfId="120" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="70"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F118">
-    <cfRule type="duplicateValues" dxfId="119" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="71"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F119">
-    <cfRule type="duplicateValues" dxfId="118" priority="64"/>
-    <cfRule type="duplicateValues" dxfId="117" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="65"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F119">
-    <cfRule type="duplicateValues" dxfId="116" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="66"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F119">
-    <cfRule type="duplicateValues" dxfId="115" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="67"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F120">
-    <cfRule type="duplicateValues" dxfId="114" priority="60"/>
-    <cfRule type="duplicateValues" dxfId="113" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="61"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F120">
-    <cfRule type="duplicateValues" dxfId="112" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="62"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F120">
-    <cfRule type="duplicateValues" dxfId="111" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="63"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F121">
-    <cfRule type="duplicateValues" dxfId="110" priority="52"/>
-    <cfRule type="duplicateValues" dxfId="109" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F121">
-    <cfRule type="duplicateValues" dxfId="108" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F121">
-    <cfRule type="duplicateValues" dxfId="107" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F122">
-    <cfRule type="duplicateValues" dxfId="106" priority="48"/>
-    <cfRule type="duplicateValues" dxfId="105" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F122">
-    <cfRule type="duplicateValues" dxfId="104" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F122">
-    <cfRule type="duplicateValues" dxfId="103" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="51"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F123">
-    <cfRule type="duplicateValues" dxfId="102" priority="44"/>
-    <cfRule type="duplicateValues" dxfId="101" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F123">
-    <cfRule type="duplicateValues" dxfId="100" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F123">
-    <cfRule type="duplicateValues" dxfId="99" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="47"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F124">
-    <cfRule type="duplicateValues" dxfId="98" priority="40"/>
-    <cfRule type="duplicateValues" dxfId="97" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F124">
-    <cfRule type="duplicateValues" dxfId="96" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F124">
-    <cfRule type="duplicateValues" dxfId="95" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F125">
-    <cfRule type="duplicateValues" dxfId="94" priority="36"/>
-    <cfRule type="duplicateValues" dxfId="93" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F125">
-    <cfRule type="duplicateValues" dxfId="92" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F125">
-    <cfRule type="duplicateValues" dxfId="91" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F126">
-    <cfRule type="duplicateValues" dxfId="90" priority="32"/>
-    <cfRule type="duplicateValues" dxfId="89" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F126">
-    <cfRule type="duplicateValues" dxfId="88" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F126">
-    <cfRule type="duplicateValues" dxfId="87" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F127">
-    <cfRule type="duplicateValues" dxfId="86" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="85" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F127">
-    <cfRule type="duplicateValues" dxfId="84" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F127">
-    <cfRule type="duplicateValues" dxfId="83" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F128">
-    <cfRule type="duplicateValues" dxfId="82" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="81" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F128">
-    <cfRule type="duplicateValues" dxfId="80" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F128">
-    <cfRule type="duplicateValues" dxfId="79" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F129">
-    <cfRule type="duplicateValues" dxfId="78" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F129">
-    <cfRule type="duplicateValues" dxfId="77" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="76" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F130">
-    <cfRule type="duplicateValues" dxfId="75" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F130">
-    <cfRule type="duplicateValues" dxfId="74" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="73" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F131">
-    <cfRule type="duplicateValues" dxfId="72" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="71" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F131">
-    <cfRule type="duplicateValues" dxfId="70" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F131">
-    <cfRule type="duplicateValues" dxfId="69" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F132">
-    <cfRule type="duplicateValues" dxfId="68" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="67" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F132">
-    <cfRule type="duplicateValues" dxfId="66" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F132">
-    <cfRule type="duplicateValues" dxfId="65" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I133:T133">
-    <cfRule type="cellIs" dxfId="64" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="5" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F133">
-    <cfRule type="duplicateValues" dxfId="63" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="62" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F133">
-    <cfRule type="duplicateValues" dxfId="61" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F133">
-    <cfRule type="duplicateValues" dxfId="60" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F137">
-    <cfRule type="duplicateValues" dxfId="59" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="58" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F137">
-    <cfRule type="duplicateValues" dxfId="57" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F137">
-    <cfRule type="duplicateValues" dxfId="56" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
